--- a/One_Piece.xlsx
+++ b/One_Piece.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\İndirilenler\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{E643E2AB-7101-4A5E-874D-B1EEDB5372FA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A36A2062-8443-488B-8BC9-210CD2D76912}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -3012,7 +3012,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -3056,30 +3056,11 @@
     <xf numFmtId="0" fontId="8" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="8">
-    <dxf>
-      <border>
-        <left style="thin">
-          <color rgb="FF356854"/>
-        </left>
-        <right style="thin">
-          <color rgb="FF356854"/>
-        </right>
-        <top style="thin">
-          <color rgb="FF356854"/>
-        </top>
-        <bottom style="thin">
-          <color rgb="FF356854"/>
-        </bottom>
-      </border>
-    </dxf>
     <dxf>
       <fill>
         <patternFill patternType="solid">
@@ -3144,19 +3125,35 @@
         </patternFill>
       </fill>
     </dxf>
+    <dxf>
+      <border>
+        <left style="thin">
+          <color rgb="FF356854"/>
+        </left>
+        <right style="thin">
+          <color rgb="FF356854"/>
+        </right>
+        <top style="thin">
+          <color rgb="FF356854"/>
+        </top>
+        <bottom style="thin">
+          <color rgb="FF356854"/>
+        </bottom>
+      </border>
+    </dxf>
   </dxfs>
   <tableStyles count="2">
     <tableStyle name="Karakterler-style" pivot="0" count="4" xr9:uid="{00000000-0011-0000-FFFF-FFFF00000000}">
-      <tableStyleElement type="wholeTable" size="0" dxfId="4"/>
-      <tableStyleElement type="headerRow" dxfId="7"/>
-      <tableStyleElement type="firstRowStripe" dxfId="6"/>
-      <tableStyleElement type="secondRowStripe" dxfId="5"/>
+      <tableStyleElement type="wholeTable" size="0" dxfId="7"/>
+      <tableStyleElement type="headerRow" dxfId="6"/>
+      <tableStyleElement type="firstRowStripe" dxfId="5"/>
+      <tableStyleElement type="secondRowStripe" dxfId="4"/>
     </tableStyle>
     <tableStyle name="Tabu-style" pivot="0" count="4" xr9:uid="{00000000-0011-0000-FFFF-FFFF01000000}">
-      <tableStyleElement type="wholeTable" size="0" dxfId="0"/>
-      <tableStyleElement type="headerRow" dxfId="3"/>
-      <tableStyleElement type="firstRowStripe" dxfId="2"/>
-      <tableStyleElement type="secondRowStripe" dxfId="1"/>
+      <tableStyleElement type="wholeTable" size="0" dxfId="3"/>
+      <tableStyleElement type="headerRow" dxfId="2"/>
+      <tableStyleElement type="firstRowStripe" dxfId="1"/>
+      <tableStyleElement type="secondRowStripe" dxfId="0"/>
     </tableStyle>
   </tableStyles>
   <extLst>
@@ -3549,7 +3546,7 @@
       <c r="Q2" s="9"/>
       <c r="R2" s="9"/>
       <c r="S2" s="11">
-        <f>IF(R2&lt;&gt;"",R2,ROUND((L2+M2+K2+IF(COUNT(N2:P2)&gt;0,AVERAGE(N2:P2),0))/(3+IF(COUNT(N2:P2)&gt;0,1,0)),1))</f>
+        <f t="shared" ref="S2:S33" si="0">IF(R2&lt;&gt;"",R2,ROUND((L2+M2+K2+IF(COUNT(N2:P2)&gt;0,AVERAGE(N2:P2),0))/(3+IF(COUNT(N2:P2)&gt;0,1,0)),1))</f>
         <v>20</v>
       </c>
       <c r="T2" s="7"/>
@@ -3565,7 +3562,7 @@
       <c r="B3" s="8" t="s">
         <v>88</v>
       </c>
-      <c r="C3" s="15">
+      <c r="C3" s="8">
         <v>4388000000</v>
       </c>
       <c r="D3" s="8" t="s">
@@ -3610,7 +3607,7 @@
         <v>19</v>
       </c>
       <c r="S3" s="11">
-        <f>IF(R3&lt;&gt;"",R3,ROUND((L3+M3+K3+IF(COUNT(N3:P3)&gt;0,AVERAGE(N3:P3),0))/(3+IF(COUNT(N3:P3)&gt;0,1,0)),1))</f>
+        <f t="shared" si="0"/>
         <v>19</v>
       </c>
       <c r="T3" s="7"/>
@@ -3671,7 +3668,7 @@
         <v>19</v>
       </c>
       <c r="S4" s="11">
-        <f>IF(R4&lt;&gt;"",R4,ROUND((L4+M4+K4+IF(COUNT(N4:P4)&gt;0,AVERAGE(N4:P4),0))/(3+IF(COUNT(N4:P4)&gt;0,1,0)),1))</f>
+        <f t="shared" si="0"/>
         <v>19</v>
       </c>
       <c r="T4" s="7"/>
@@ -3687,7 +3684,7 @@
       <c r="B5" s="8" t="s">
         <v>105</v>
       </c>
-      <c r="C5" s="15">
+      <c r="C5" s="8">
         <v>5046000000</v>
       </c>
       <c r="D5" s="8" t="s">
@@ -3732,7 +3729,7 @@
         <v>19</v>
       </c>
       <c r="S5" s="11">
-        <f>IF(R5&lt;&gt;"",R5,ROUND((L5+M5+K5+IF(COUNT(N5:P5)&gt;0,AVERAGE(N5:P5),0))/(3+IF(COUNT(N5:P5)&gt;0,1,0)),1))</f>
+        <f t="shared" si="0"/>
         <v>19</v>
       </c>
       <c r="T5" s="7"/>
@@ -3789,7 +3786,7 @@
         <v>19</v>
       </c>
       <c r="S6" s="11">
-        <f>IF(R6&lt;&gt;"",R6,ROUND((L6+M6+K6+IF(COUNT(N6:P6)&gt;0,AVERAGE(N6:P6),0))/(3+IF(COUNT(N6:P6)&gt;0,1,0)),1))</f>
+        <f t="shared" si="0"/>
         <v>19</v>
       </c>
       <c r="T6" s="7"/>
@@ -3848,7 +3845,7 @@
         <v>19</v>
       </c>
       <c r="S7" s="11">
-        <f>IF(R7&lt;&gt;"",R7,ROUND((L7+M7+K7+IF(COUNT(N7:P7)&gt;0,AVERAGE(N7:P7),0))/(3+IF(COUNT(N7:P7)&gt;0,1,0)),1))</f>
+        <f t="shared" si="0"/>
         <v>19</v>
       </c>
       <c r="T7" s="7"/>
@@ -3907,7 +3904,7 @@
         <v>19</v>
       </c>
       <c r="S8" s="11">
-        <f>IF(R8&lt;&gt;"",R8,ROUND((L8+M8+K8+IF(COUNT(N8:P8)&gt;0,AVERAGE(N8:P8),0))/(3+IF(COUNT(N8:P8)&gt;0,1,0)),1))</f>
+        <f t="shared" si="0"/>
         <v>19</v>
       </c>
       <c r="T8" s="7"/>
@@ -3966,7 +3963,7 @@
         <v>19</v>
       </c>
       <c r="S9" s="11">
-        <f>IF(R9&lt;&gt;"",R9,ROUND((L9+M9+K9+IF(COUNT(N9:P9)&gt;0,AVERAGE(N9:P9),0))/(3+IF(COUNT(N9:P9)&gt;0,1,0)),1))</f>
+        <f t="shared" si="0"/>
         <v>19</v>
       </c>
       <c r="T9" s="7"/>
@@ -4025,7 +4022,7 @@
         <v>19</v>
       </c>
       <c r="S10" s="11">
-        <f>IF(R10&lt;&gt;"",R10,ROUND((L10+M10+K10+IF(COUNT(N10:P10)&gt;0,AVERAGE(N10:P10),0))/(3+IF(COUNT(N10:P10)&gt;0,1,0)),1))</f>
+        <f t="shared" si="0"/>
         <v>19</v>
       </c>
       <c r="T10" s="7"/>
@@ -4080,7 +4077,7 @@
       <c r="Q11" s="9"/>
       <c r="R11" s="9"/>
       <c r="S11" s="11">
-        <f>IF(R11&lt;&gt;"",R11,ROUND((L11+M11+K11+IF(COUNT(N11:P11)&gt;0,AVERAGE(N11:P11),0))/(3+IF(COUNT(N11:P11)&gt;0,1,0)),1))</f>
+        <f t="shared" si="0"/>
         <v>18.7</v>
       </c>
       <c r="T11" s="7"/>
@@ -4135,7 +4132,7 @@
         <v>18</v>
       </c>
       <c r="S12" s="11">
-        <f>IF(R12&lt;&gt;"",R12,ROUND((L12+M12+K12+IF(COUNT(N12:P12)&gt;0,AVERAGE(N12:P12),0))/(3+IF(COUNT(N12:P12)&gt;0,1,0)),1))</f>
+        <f t="shared" si="0"/>
         <v>18</v>
       </c>
       <c r="T12" s="7"/>
@@ -4194,7 +4191,7 @@
         <v>18</v>
       </c>
       <c r="S13" s="11">
-        <f>IF(R13&lt;&gt;"",R13,ROUND((L13+M13+K13+IF(COUNT(N13:P13)&gt;0,AVERAGE(N13:P13),0))/(3+IF(COUNT(N13:P13)&gt;0,1,0)),1))</f>
+        <f t="shared" si="0"/>
         <v>18</v>
       </c>
       <c r="T13" s="7"/>
@@ -4251,7 +4248,7 @@
         <v>17</v>
       </c>
       <c r="S14" s="11">
-        <f>IF(R14&lt;&gt;"",R14,ROUND((L14+M14+K14+IF(COUNT(N14:P14)&gt;0,AVERAGE(N14:P14),0))/(3+IF(COUNT(N14:P14)&gt;0,1,0)),1))</f>
+        <f t="shared" si="0"/>
         <v>17</v>
       </c>
       <c r="T14" s="7"/>
@@ -4308,7 +4305,7 @@
       </c>
       <c r="R15" s="9"/>
       <c r="S15" s="11">
-        <f>IF(R15&lt;&gt;"",R15,ROUND((L15+M15+K15+IF(COUNT(N15:P15)&gt;0,AVERAGE(N15:P15),0))/(3+IF(COUNT(N15:P15)&gt;0,1,0)),1))</f>
+        <f t="shared" si="0"/>
         <v>16.3</v>
       </c>
       <c r="T15" s="7"/>
@@ -4365,7 +4362,7 @@
         <v>16</v>
       </c>
       <c r="S16" s="11">
-        <f>IF(R16&lt;&gt;"",R16,ROUND((L16+M16+K16+IF(COUNT(N16:P16)&gt;0,AVERAGE(N16:P16),0))/(3+IF(COUNT(N16:P16)&gt;0,1,0)),1))</f>
+        <f t="shared" si="0"/>
         <v>16</v>
       </c>
       <c r="T16" s="7"/>
@@ -4426,7 +4423,7 @@
         <v>16</v>
       </c>
       <c r="S17" s="11">
-        <f>IF(R17&lt;&gt;"",R17,ROUND((L17+M17+K17+IF(COUNT(N17:P17)&gt;0,AVERAGE(N17:P17),0))/(3+IF(COUNT(N17:P17)&gt;0,1,0)),1))</f>
+        <f t="shared" si="0"/>
         <v>16</v>
       </c>
       <c r="T17" s="7"/>
@@ -4485,7 +4482,7 @@
       </c>
       <c r="R18" s="9"/>
       <c r="S18" s="11">
-        <f>IF(R18&lt;&gt;"",R18,ROUND((L18+M18+K18+IF(COUNT(N18:P18)&gt;0,AVERAGE(N18:P18),0))/(3+IF(COUNT(N18:P18)&gt;0,1,0)),1))</f>
+        <f t="shared" si="0"/>
         <v>16</v>
       </c>
       <c r="T18" s="7"/>
@@ -4544,7 +4541,7 @@
         <v>16</v>
       </c>
       <c r="S19" s="11">
-        <f>IF(R19&lt;&gt;"",R19,ROUND((L19+M19+K19+IF(COUNT(N19:P19)&gt;0,AVERAGE(N19:P19),0))/(3+IF(COUNT(N19:P19)&gt;0,1,0)),1))</f>
+        <f t="shared" si="0"/>
         <v>16</v>
       </c>
       <c r="T19" s="7"/>
@@ -4560,7 +4557,7 @@
       <c r="B20" s="8" t="s">
         <v>252</v>
       </c>
-      <c r="C20" s="15">
+      <c r="C20" s="8">
         <v>1659000000</v>
       </c>
       <c r="D20" s="8" t="s">
@@ -4605,7 +4602,7 @@
         <v>16</v>
       </c>
       <c r="S20" s="11">
-        <f>IF(R20&lt;&gt;"",R20,ROUND((L20+M20+K20+IF(COUNT(N20:P20)&gt;0,AVERAGE(N20:P20),0))/(3+IF(COUNT(N20:P20)&gt;0,1,0)),1))</f>
+        <f t="shared" si="0"/>
         <v>16</v>
       </c>
       <c r="T20" s="7"/>
@@ -4621,7 +4618,7 @@
       <c r="B21" s="8" t="s">
         <v>358</v>
       </c>
-      <c r="C21" s="15" t="s">
+      <c r="C21" s="8" t="s">
         <v>36</v>
       </c>
       <c r="D21" s="8" t="s">
@@ -4662,7 +4659,7 @@
         <v>16</v>
       </c>
       <c r="S21" s="11">
-        <f>IF(R21&lt;&gt;"",R21,ROUND((L21+M21+K21+IF(COUNT(N21:P21)&gt;0,AVERAGE(N21:P21),0))/(3+IF(COUNT(N21:P21)&gt;0,1,0)),1))</f>
+        <f t="shared" si="0"/>
         <v>16</v>
       </c>
       <c r="T21" s="7"/>
@@ -4721,7 +4718,7 @@
         <v>16</v>
       </c>
       <c r="S22" s="11">
-        <f>IF(R22&lt;&gt;"",R22,ROUND((L22+M22+K22+IF(COUNT(N22:P22)&gt;0,AVERAGE(N22:P22),0))/(3+IF(COUNT(N22:P22)&gt;0,1,0)),1))</f>
+        <f t="shared" si="0"/>
         <v>16</v>
       </c>
       <c r="T22" s="7"/>
@@ -4780,7 +4777,7 @@
       </c>
       <c r="R23" s="9"/>
       <c r="S23" s="11">
-        <f>IF(R23&lt;&gt;"",R23,ROUND((L23+M23+K23+IF(COUNT(N23:P23)&gt;0,AVERAGE(N23:P23),0))/(3+IF(COUNT(N23:P23)&gt;0,1,0)),1))</f>
+        <f t="shared" si="0"/>
         <v>16</v>
       </c>
       <c r="T23" s="7"/>
@@ -4839,7 +4836,7 @@
       </c>
       <c r="R24" s="9"/>
       <c r="S24" s="11">
-        <f>IF(R24&lt;&gt;"",R24,ROUND((L24+M24+K24+IF(COUNT(N24:P24)&gt;0,AVERAGE(N24:P24),0))/(3+IF(COUNT(N24:P24)&gt;0,1,0)),1))</f>
+        <f t="shared" si="0"/>
         <v>15.3</v>
       </c>
       <c r="T24" s="7"/>
@@ -4896,7 +4893,7 @@
       </c>
       <c r="R25" s="9"/>
       <c r="S25" s="11">
-        <f>IF(R25&lt;&gt;"",R25,ROUND((L25+M25+K25+IF(COUNT(N25:P25)&gt;0,AVERAGE(N25:P25),0))/(3+IF(COUNT(N25:P25)&gt;0,1,0)),1))</f>
+        <f t="shared" si="0"/>
         <v>15</v>
       </c>
       <c r="T25" s="7"/>
@@ -4912,7 +4909,7 @@
       <c r="B26" s="8" t="s">
         <v>237</v>
       </c>
-      <c r="C26" s="15">
+      <c r="C26" s="8">
         <v>1800000000</v>
       </c>
       <c r="D26" s="8" t="s">
@@ -4953,7 +4950,7 @@
       </c>
       <c r="R26" s="9"/>
       <c r="S26" s="11">
-        <f>IF(R26&lt;&gt;"",R26,ROUND((L26+M26+K26+IF(COUNT(N26:P26)&gt;0,AVERAGE(N26:P26),0))/(3+IF(COUNT(N26:P26)&gt;0,1,0)),1))</f>
+        <f t="shared" si="0"/>
         <v>15</v>
       </c>
       <c r="T26" s="7"/>
@@ -5014,7 +5011,7 @@
         <v>16</v>
       </c>
       <c r="S27" s="11">
-        <f>IF(R27&lt;&gt;"",R27,ROUND((L27+M27+K27+IF(COUNT(N27:P27)&gt;0,AVERAGE(N27:P27),0))/(3+IF(COUNT(N27:P27)&gt;0,1,0)),1))</f>
+        <f t="shared" si="0"/>
         <v>16</v>
       </c>
       <c r="T27" s="7"/>
@@ -5071,7 +5068,7 @@
         <v>17</v>
       </c>
       <c r="S28" s="11">
-        <f>IF(R28&lt;&gt;"",R28,ROUND((L28+M28+K28+IF(COUNT(N28:P28)&gt;0,AVERAGE(N28:P28),0))/(3+IF(COUNT(N28:P28)&gt;0,1,0)),1))</f>
+        <f t="shared" si="0"/>
         <v>17</v>
       </c>
       <c r="T28" s="7"/>
@@ -5130,7 +5127,7 @@
         <v>16</v>
       </c>
       <c r="S29" s="11">
-        <f>IF(R29&lt;&gt;"",R29,ROUND((L29+M29+K29+IF(COUNT(N29:P29)&gt;0,AVERAGE(N29:P29),0))/(3+IF(COUNT(N29:P29)&gt;0,1,0)),1))</f>
+        <f t="shared" si="0"/>
         <v>16</v>
       </c>
       <c r="T29" s="7"/>
@@ -5189,7 +5186,7 @@
         <v>16</v>
       </c>
       <c r="S30" s="11">
-        <f>IF(R30&lt;&gt;"",R30,ROUND((L30+M30+K30+IF(COUNT(N30:P30)&gt;0,AVERAGE(N30:P30),0))/(3+IF(COUNT(N30:P30)&gt;0,1,0)),1))</f>
+        <f t="shared" si="0"/>
         <v>16</v>
       </c>
       <c r="T30" s="7"/>
@@ -5248,7 +5245,7 @@
         <v>16</v>
       </c>
       <c r="S31" s="11">
-        <f>IF(R31&lt;&gt;"",R31,ROUND((L31+M31+K31+IF(COUNT(N31:P31)&gt;0,AVERAGE(N31:P31),0))/(3+IF(COUNT(N31:P31)&gt;0,1,0)),1))</f>
+        <f t="shared" si="0"/>
         <v>16</v>
       </c>
       <c r="T31" s="7"/>
@@ -5307,7 +5304,7 @@
         <v>16</v>
       </c>
       <c r="S32" s="11">
-        <f>IF(R32&lt;&gt;"",R32,ROUND((L32+M32+K32+IF(COUNT(N32:P32)&gt;0,AVERAGE(N32:P32),0))/(3+IF(COUNT(N32:P32)&gt;0,1,0)),1))</f>
+        <f t="shared" si="0"/>
         <v>16</v>
       </c>
       <c r="T32" s="7"/>
@@ -5323,7 +5320,7 @@
       <c r="B33" s="8" t="s">
         <v>37</v>
       </c>
-      <c r="C33" s="15">
+      <c r="C33" s="8">
         <v>1111000000</v>
       </c>
       <c r="D33" s="8" t="s">
@@ -5364,7 +5361,7 @@
       </c>
       <c r="R33" s="9"/>
       <c r="S33" s="11">
-        <f>IF(R33&lt;&gt;"",R33,ROUND((L33+M33+K33+IF(COUNT(N33:P33)&gt;0,AVERAGE(N33:P33),0))/(3+IF(COUNT(N33:P33)&gt;0,1,0)),1))</f>
+        <f t="shared" si="0"/>
         <v>14</v>
       </c>
       <c r="T33" s="7"/>
@@ -5421,7 +5418,7 @@
       <c r="Q34" s="9"/>
       <c r="R34" s="9"/>
       <c r="S34" s="11">
-        <f>IF(R34&lt;&gt;"",R34,ROUND((L34+M34+K34+IF(COUNT(N34:P34)&gt;0,AVERAGE(N34:P34),0))/(3+IF(COUNT(N34:P34)&gt;0,1,0)),1))</f>
+        <f t="shared" ref="S34:S65" si="1">IF(R34&lt;&gt;"",R34,ROUND((L34+M34+K34+IF(COUNT(N34:P34)&gt;0,AVERAGE(N34:P34),0))/(3+IF(COUNT(N34:P34)&gt;0,1,0)),1))</f>
         <v>14</v>
       </c>
       <c r="T34" s="7"/>
@@ -5437,10 +5434,10 @@
       <c r="B35" s="8" t="s">
         <v>319</v>
       </c>
-      <c r="C35" s="15">
+      <c r="C35" s="8">
         <v>3000000000</v>
       </c>
-      <c r="D35" s="15" t="s">
+      <c r="D35" s="8" t="s">
         <v>24</v>
       </c>
       <c r="E35" s="8" t="s">
@@ -5480,7 +5477,7 @@
       </c>
       <c r="R35" s="9"/>
       <c r="S35" s="11">
-        <f>IF(R35&lt;&gt;"",R35,ROUND((L35+M35+K35+IF(COUNT(N35:P35)&gt;0,AVERAGE(N35:P35),0))/(3+IF(COUNT(N35:P35)&gt;0,1,0)),1))</f>
+        <f t="shared" si="1"/>
         <v>14</v>
       </c>
       <c r="T35" s="7"/>
@@ -5541,7 +5538,7 @@
       </c>
       <c r="R36" s="9"/>
       <c r="S36" s="11">
-        <f>IF(R36&lt;&gt;"",R36,ROUND((L36+M36+K36+IF(COUNT(N36:P36)&gt;0,AVERAGE(N36:P36),0))/(3+IF(COUNT(N36:P36)&gt;0,1,0)),1))</f>
+        <f t="shared" si="1"/>
         <v>13.9</v>
       </c>
       <c r="T36" s="7"/>
@@ -5600,7 +5597,7 @@
       </c>
       <c r="R37" s="9"/>
       <c r="S37" s="11">
-        <f>IF(R37&lt;&gt;"",R37,ROUND((L37+M37+K37+IF(COUNT(N37:P37)&gt;0,AVERAGE(N37:P37),0))/(3+IF(COUNT(N37:P37)&gt;0,1,0)),1))</f>
+        <f t="shared" si="1"/>
         <v>13.8</v>
       </c>
       <c r="T37" s="7"/>
@@ -5616,7 +5613,7 @@
       <c r="B38" s="8" t="s">
         <v>236</v>
       </c>
-      <c r="C38" s="15">
+      <c r="C38" s="8">
         <v>1374000000</v>
       </c>
       <c r="D38" s="8" t="s">
@@ -5659,7 +5656,7 @@
       </c>
       <c r="R38" s="9"/>
       <c r="S38" s="11">
-        <f>IF(R38&lt;&gt;"",R38,ROUND((L38+M38+K38+IF(COUNT(N38:P38)&gt;0,AVERAGE(N38:P38),0))/(3+IF(COUNT(N38:P38)&gt;0,1,0)),1))</f>
+        <f t="shared" si="1"/>
         <v>13.8</v>
       </c>
       <c r="T38" s="7"/>
@@ -5675,7 +5672,7 @@
       <c r="B39" s="8" t="s">
         <v>226</v>
       </c>
-      <c r="C39" s="15">
+      <c r="C39" s="8">
         <v>3590000000</v>
       </c>
       <c r="D39" s="8" t="s">
@@ -5718,7 +5715,7 @@
         <v>17</v>
       </c>
       <c r="S39" s="11">
-        <f>IF(R39&lt;&gt;"",R39,ROUND((L39+M39+K39+IF(COUNT(N39:P39)&gt;0,AVERAGE(N39:P39),0))/(3+IF(COUNT(N39:P39)&gt;0,1,0)),1))</f>
+        <f t="shared" si="1"/>
         <v>17</v>
       </c>
       <c r="T39" s="7"/>
@@ -5777,7 +5774,7 @@
       </c>
       <c r="R40" s="9"/>
       <c r="S40" s="11">
-        <f>IF(R40&lt;&gt;"",R40,ROUND((L40+M40+K40+IF(COUNT(N40:P40)&gt;0,AVERAGE(N40:P40),0))/(3+IF(COUNT(N40:P40)&gt;0,1,0)),1))</f>
+        <f t="shared" si="1"/>
         <v>13.5</v>
       </c>
       <c r="T40" s="7"/>
@@ -5834,7 +5831,7 @@
       <c r="Q41" s="9"/>
       <c r="R41" s="9"/>
       <c r="S41" s="11">
-        <f>IF(R41&lt;&gt;"",R41,ROUND((L41+M41+K41+IF(COUNT(N41:P41)&gt;0,AVERAGE(N41:P41),0))/(3+IF(COUNT(N41:P41)&gt;0,1,0)),1))</f>
+        <f t="shared" si="1"/>
         <v>13.5</v>
       </c>
       <c r="T41" s="7"/>
@@ -5891,7 +5888,7 @@
       </c>
       <c r="R42" s="9"/>
       <c r="S42" s="11">
-        <f>IF(R42&lt;&gt;"",R42,ROUND((L42+M42+K42+IF(COUNT(N42:P42)&gt;0,AVERAGE(N42:P42),0))/(3+IF(COUNT(N42:P42)&gt;0,1,0)),1))</f>
+        <f t="shared" si="1"/>
         <v>13.3</v>
       </c>
       <c r="T42" s="7"/>
@@ -5948,7 +5945,7 @@
       <c r="Q43" s="9"/>
       <c r="R43" s="9"/>
       <c r="S43" s="11">
-        <f>IF(R43&lt;&gt;"",R43,ROUND((L43+M43+K43+IF(COUNT(N43:P43)&gt;0,AVERAGE(N43:P43),0))/(3+IF(COUNT(N43:P43)&gt;0,1,0)),1))</f>
+        <f t="shared" si="1"/>
         <v>13.3</v>
       </c>
       <c r="T43" s="7"/>
@@ -6007,7 +6004,7 @@
       </c>
       <c r="R44" s="9"/>
       <c r="S44" s="11">
-        <f>IF(R44&lt;&gt;"",R44,ROUND((L44+M44+K44+IF(COUNT(N44:P44)&gt;0,AVERAGE(N44:P44),0))/(3+IF(COUNT(N44:P44)&gt;0,1,0)),1))</f>
+        <f t="shared" si="1"/>
         <v>13.3</v>
       </c>
       <c r="T44" s="7"/>
@@ -6066,7 +6063,7 @@
       </c>
       <c r="R45" s="9"/>
       <c r="S45" s="11">
-        <f>IF(R45&lt;&gt;"",R45,ROUND((L45+M45+K45+IF(COUNT(N45:P45)&gt;0,AVERAGE(N45:P45),0))/(3+IF(COUNT(N45:P45)&gt;0,1,0)),1))</f>
+        <f t="shared" si="1"/>
         <v>13.3</v>
       </c>
       <c r="T45" s="7"/>
@@ -6125,7 +6122,7 @@
         <v>15</v>
       </c>
       <c r="S46" s="11">
-        <f>IF(R46&lt;&gt;"",R46,ROUND((L46+M46+K46+IF(COUNT(N46:P46)&gt;0,AVERAGE(N46:P46),0))/(3+IF(COUNT(N46:P46)&gt;0,1,0)),1))</f>
+        <f t="shared" si="1"/>
         <v>15</v>
       </c>
       <c r="T46" s="7"/>
@@ -6182,7 +6179,7 @@
       <c r="Q47" s="9"/>
       <c r="R47" s="9"/>
       <c r="S47" s="11">
-        <f>IF(R47&lt;&gt;"",R47,ROUND((L47+M47+K47+IF(COUNT(N47:P47)&gt;0,AVERAGE(N47:P47),0))/(3+IF(COUNT(N47:P47)&gt;0,1,0)),1))</f>
+        <f t="shared" si="1"/>
         <v>13</v>
       </c>
       <c r="T47" s="7"/>
@@ -6241,7 +6238,7 @@
       </c>
       <c r="R48" s="9"/>
       <c r="S48" s="11">
-        <f>IF(R48&lt;&gt;"",R48,ROUND((L48+M48+K48+IF(COUNT(N48:P48)&gt;0,AVERAGE(N48:P48),0))/(3+IF(COUNT(N48:P48)&gt;0,1,0)),1))</f>
+        <f t="shared" si="1"/>
         <v>12.5</v>
       </c>
       <c r="T48" s="7"/>
@@ -6302,7 +6299,7 @@
         <v>15</v>
       </c>
       <c r="S49" s="11">
-        <f>IF(R49&lt;&gt;"",R49,ROUND((L49+M49+K49+IF(COUNT(N49:P49)&gt;0,AVERAGE(N49:P49),0))/(3+IF(COUNT(N49:P49)&gt;0,1,0)),1))</f>
+        <f t="shared" si="1"/>
         <v>15</v>
       </c>
       <c r="T49" s="7"/>
@@ -6361,7 +6358,7 @@
         <v>16</v>
       </c>
       <c r="S50" s="11">
-        <f>IF(R50&lt;&gt;"",R50,ROUND((L50+M50+K50+IF(COUNT(N50:P50)&gt;0,AVERAGE(N50:P50),0))/(3+IF(COUNT(N50:P50)&gt;0,1,0)),1))</f>
+        <f t="shared" si="1"/>
         <v>16</v>
       </c>
       <c r="T50" s="7"/>
@@ -6418,7 +6415,7 @@
       <c r="Q51" s="9"/>
       <c r="R51" s="9"/>
       <c r="S51" s="11">
-        <f>IF(R51&lt;&gt;"",R51,ROUND((L51+M51+K51+IF(COUNT(N51:P51)&gt;0,AVERAGE(N51:P51),0))/(3+IF(COUNT(N51:P51)&gt;0,1,0)),1))</f>
+        <f t="shared" si="1"/>
         <v>12.5</v>
       </c>
       <c r="T51" s="7"/>
@@ -6477,7 +6474,7 @@
       </c>
       <c r="R52" s="9"/>
       <c r="S52" s="11">
-        <f>IF(R52&lt;&gt;"",R52,ROUND((L52+M52+K52+IF(COUNT(N52:P52)&gt;0,AVERAGE(N52:P52),0))/(3+IF(COUNT(N52:P52)&gt;0,1,0)),1))</f>
+        <f t="shared" si="1"/>
         <v>12.5</v>
       </c>
       <c r="T52" s="7"/>
@@ -6532,7 +6529,7 @@
       <c r="Q53" s="9"/>
       <c r="R53" s="9"/>
       <c r="S53" s="11">
-        <f>IF(R53&lt;&gt;"",R53,ROUND((L53+M53+K53+IF(COUNT(N53:P53)&gt;0,AVERAGE(N53:P53),0))/(3+IF(COUNT(N53:P53)&gt;0,1,0)),1))</f>
+        <f t="shared" si="1"/>
         <v>12.3</v>
       </c>
       <c r="T53" s="7"/>
@@ -6589,7 +6586,7 @@
       </c>
       <c r="R54" s="9"/>
       <c r="S54" s="11">
-        <f>IF(R54&lt;&gt;"",R54,ROUND((L54+M54+K54+IF(COUNT(N54:P54)&gt;0,AVERAGE(N54:P54),0))/(3+IF(COUNT(N54:P54)&gt;0,1,0)),1))</f>
+        <f t="shared" si="1"/>
         <v>12</v>
       </c>
       <c r="T54" s="7"/>
@@ -6646,7 +6643,7 @@
         <v>14</v>
       </c>
       <c r="S55" s="11">
-        <f>IF(R55&lt;&gt;"",R55,ROUND((L55+M55+K55+IF(COUNT(N55:P55)&gt;0,AVERAGE(N55:P55),0))/(3+IF(COUNT(N55:P55)&gt;0,1,0)),1))</f>
+        <f t="shared" si="1"/>
         <v>14</v>
       </c>
       <c r="T55" s="7"/>
@@ -6662,7 +6659,7 @@
       <c r="B56" s="8" t="s">
         <v>498</v>
       </c>
-      <c r="C56" s="15" t="s">
+      <c r="C56" s="8" t="s">
         <v>36</v>
       </c>
       <c r="D56" s="8" t="s">
@@ -6703,7 +6700,7 @@
         <v>14</v>
       </c>
       <c r="S56" s="11">
-        <f>IF(R56&lt;&gt;"",R56,ROUND((L56+M56+K56+IF(COUNT(N56:P56)&gt;0,AVERAGE(N56:P56),0))/(3+IF(COUNT(N56:P56)&gt;0,1,0)),1))</f>
+        <f t="shared" si="1"/>
         <v>14</v>
       </c>
       <c r="T56" s="7"/>
@@ -6760,7 +6757,7 @@
       <c r="Q57" s="9"/>
       <c r="R57" s="9"/>
       <c r="S57" s="11">
-        <f>IF(R57&lt;&gt;"",R57,ROUND((L57+M57+K57+IF(COUNT(N57:P57)&gt;0,AVERAGE(N57:P57),0))/(3+IF(COUNT(N57:P57)&gt;0,1,0)),1))</f>
+        <f t="shared" si="1"/>
         <v>11.8</v>
       </c>
       <c r="T57" s="7"/>
@@ -6817,7 +6814,7 @@
       </c>
       <c r="R58" s="9"/>
       <c r="S58" s="11">
-        <f>IF(R58&lt;&gt;"",R58,ROUND((L58+M58+K58+IF(COUNT(N58:P58)&gt;0,AVERAGE(N58:P58),0))/(3+IF(COUNT(N58:P58)&gt;0,1,0)),1))</f>
+        <f t="shared" si="1"/>
         <v>11.7</v>
       </c>
       <c r="T58" s="7"/>
@@ -6872,7 +6869,7 @@
       <c r="Q59" s="9"/>
       <c r="R59" s="9"/>
       <c r="S59" s="11">
-        <f>IF(R59&lt;&gt;"",R59,ROUND((L59+M59+K59+IF(COUNT(N59:P59)&gt;0,AVERAGE(N59:P59),0))/(3+IF(COUNT(N59:P59)&gt;0,1,0)),1))</f>
+        <f t="shared" si="1"/>
         <v>11.7</v>
       </c>
       <c r="T59" s="7"/>
@@ -6931,7 +6928,7 @@
       </c>
       <c r="R60" s="9"/>
       <c r="S60" s="11">
-        <f>IF(R60&lt;&gt;"",R60,ROUND((L60+M60+K60+IF(COUNT(N60:P60)&gt;0,AVERAGE(N60:P60),0))/(3+IF(COUNT(N60:P60)&gt;0,1,0)),1))</f>
+        <f t="shared" si="1"/>
         <v>11.5</v>
       </c>
       <c r="T60" s="7"/>
@@ -6990,7 +6987,7 @@
       </c>
       <c r="R61" s="9"/>
       <c r="S61" s="11">
-        <f>IF(R61&lt;&gt;"",R61,ROUND((L61+M61+K61+IF(COUNT(N61:P61)&gt;0,AVERAGE(N61:P61),0))/(3+IF(COUNT(N61:P61)&gt;0,1,0)),1))</f>
+        <f t="shared" si="1"/>
         <v>11.5</v>
       </c>
       <c r="T61" s="7"/>
@@ -7049,7 +7046,7 @@
       </c>
       <c r="R62" s="9"/>
       <c r="S62" s="11">
-        <f>IF(R62&lt;&gt;"",R62,ROUND((L62+M62+K62+IF(COUNT(N62:P62)&gt;0,AVERAGE(N62:P62),0))/(3+IF(COUNT(N62:P62)&gt;0,1,0)),1))</f>
+        <f t="shared" si="1"/>
         <v>11.5</v>
       </c>
       <c r="T62" s="7"/>
@@ -7106,7 +7103,7 @@
       <c r="Q63" s="9"/>
       <c r="R63" s="9"/>
       <c r="S63" s="11">
-        <f>IF(R63&lt;&gt;"",R63,ROUND((L63+M63+K63+IF(COUNT(N63:P63)&gt;0,AVERAGE(N63:P63),0))/(3+IF(COUNT(N63:P63)&gt;0,1,0)),1))</f>
+        <f t="shared" si="1"/>
         <v>11.5</v>
       </c>
       <c r="T63" s="7"/>
@@ -7165,7 +7162,7 @@
       </c>
       <c r="R64" s="9"/>
       <c r="S64" s="11">
-        <f>IF(R64&lt;&gt;"",R64,ROUND((L64+M64+K64+IF(COUNT(N64:P64)&gt;0,AVERAGE(N64:P64),0))/(3+IF(COUNT(N64:P64)&gt;0,1,0)),1))</f>
+        <f t="shared" si="1"/>
         <v>11.3</v>
       </c>
       <c r="T64" s="7"/>
@@ -7224,7 +7221,7 @@
       </c>
       <c r="R65" s="9"/>
       <c r="S65" s="11">
-        <f>IF(R65&lt;&gt;"",R65,ROUND((L65+M65+K65+IF(COUNT(N65:P65)&gt;0,AVERAGE(N65:P65),0))/(3+IF(COUNT(N65:P65)&gt;0,1,0)),1))</f>
+        <f t="shared" si="1"/>
         <v>11.3</v>
       </c>
       <c r="T65" s="7"/>
@@ -7281,7 +7278,7 @@
       </c>
       <c r="R66" s="9"/>
       <c r="S66" s="11">
-        <f>IF(R66&lt;&gt;"",R66,ROUND((L66+M66+K66+IF(COUNT(N66:P66)&gt;0,AVERAGE(N66:P66),0))/(3+IF(COUNT(N66:P66)&gt;0,1,0)),1))</f>
+        <f t="shared" ref="S66:S97" si="2">IF(R66&lt;&gt;"",R66,ROUND((L66+M66+K66+IF(COUNT(N66:P66)&gt;0,AVERAGE(N66:P66),0))/(3+IF(COUNT(N66:P66)&gt;0,1,0)),1))</f>
         <v>11.3</v>
       </c>
       <c r="T66" s="7"/>
@@ -7340,7 +7337,7 @@
       </c>
       <c r="R67" s="9"/>
       <c r="S67" s="11">
-        <f>IF(R67&lt;&gt;"",R67,ROUND((L67+M67+K67+IF(COUNT(N67:P67)&gt;0,AVERAGE(N67:P67),0))/(3+IF(COUNT(N67:P67)&gt;0,1,0)),1))</f>
+        <f t="shared" si="2"/>
         <v>11.3</v>
       </c>
       <c r="T67" s="7"/>
@@ -7397,7 +7394,7 @@
       </c>
       <c r="R68" s="9"/>
       <c r="S68" s="11">
-        <f>IF(R68&lt;&gt;"",R68,ROUND((L68+M68+K68+IF(COUNT(N68:P68)&gt;0,AVERAGE(N68:P68),0))/(3+IF(COUNT(N68:P68)&gt;0,1,0)),1))</f>
+        <f t="shared" si="2"/>
         <v>11.3</v>
       </c>
       <c r="T68" s="7"/>
@@ -7452,7 +7449,7 @@
       <c r="Q69" s="9"/>
       <c r="R69" s="9"/>
       <c r="S69" s="11">
-        <f>IF(R69&lt;&gt;"",R69,ROUND((L69+M69+K69+IF(COUNT(N69:P69)&gt;0,AVERAGE(N69:P69),0))/(3+IF(COUNT(N69:P69)&gt;0,1,0)),1))</f>
+        <f t="shared" si="2"/>
         <v>11.3</v>
       </c>
       <c r="T69" s="7"/>
@@ -7511,7 +7508,7 @@
       </c>
       <c r="R70" s="9"/>
       <c r="S70" s="11">
-        <f>IF(R70&lt;&gt;"",R70,ROUND((L70+M70+K70+IF(COUNT(N70:P70)&gt;0,AVERAGE(N70:P70),0))/(3+IF(COUNT(N70:P70)&gt;0,1,0)),1))</f>
+        <f t="shared" si="2"/>
         <v>11.3</v>
       </c>
       <c r="T70" s="7"/>
@@ -7566,7 +7563,7 @@
       <c r="Q71" s="9"/>
       <c r="R71" s="9"/>
       <c r="S71" s="11">
-        <f>IF(R71&lt;&gt;"",R71,ROUND((L71+M71+K71+IF(COUNT(N71:P71)&gt;0,AVERAGE(N71:P71),0))/(3+IF(COUNT(N71:P71)&gt;0,1,0)),1))</f>
+        <f t="shared" si="2"/>
         <v>11</v>
       </c>
       <c r="T71" s="7"/>
@@ -7623,7 +7620,7 @@
       <c r="Q72" s="9"/>
       <c r="R72" s="9"/>
       <c r="S72" s="11">
-        <f>IF(R72&lt;&gt;"",R72,ROUND((L72+M72+K72+IF(COUNT(N72:P72)&gt;0,AVERAGE(N72:P72),0))/(3+IF(COUNT(N72:P72)&gt;0,1,0)),1))</f>
+        <f t="shared" si="2"/>
         <v>11</v>
       </c>
       <c r="T72" s="7"/>
@@ -7678,7 +7675,7 @@
       <c r="Q73" s="9"/>
       <c r="R73" s="9"/>
       <c r="S73" s="11">
-        <f>IF(R73&lt;&gt;"",R73,ROUND((L73+M73+K73+IF(COUNT(N73:P73)&gt;0,AVERAGE(N73:P73),0))/(3+IF(COUNT(N73:P73)&gt;0,1,0)),1))</f>
+        <f t="shared" si="2"/>
         <v>11</v>
       </c>
       <c r="T73" s="7"/>
@@ -7735,7 +7732,7 @@
       <c r="Q74" s="9"/>
       <c r="R74" s="9"/>
       <c r="S74" s="11">
-        <f>IF(R74&lt;&gt;"",R74,ROUND((L74+M74+K74+IF(COUNT(N74:P74)&gt;0,AVERAGE(N74:P74),0))/(3+IF(COUNT(N74:P74)&gt;0,1,0)),1))</f>
+        <f t="shared" si="2"/>
         <v>11</v>
       </c>
       <c r="T74" s="7"/>
@@ -7794,7 +7791,7 @@
       </c>
       <c r="R75" s="9"/>
       <c r="S75" s="11">
-        <f>IF(R75&lt;&gt;"",R75,ROUND((L75+M75+K75+IF(COUNT(N75:P75)&gt;0,AVERAGE(N75:P75),0))/(3+IF(COUNT(N75:P75)&gt;0,1,0)),1))</f>
+        <f t="shared" si="2"/>
         <v>11</v>
       </c>
       <c r="T75" s="7"/>
@@ -7851,7 +7848,7 @@
       <c r="Q76" s="9"/>
       <c r="R76" s="9"/>
       <c r="S76" s="11">
-        <f>IF(R76&lt;&gt;"",R76,ROUND((L76+M76+K76+IF(COUNT(N76:P76)&gt;0,AVERAGE(N76:P76),0))/(3+IF(COUNT(N76:P76)&gt;0,1,0)),1))</f>
+        <f t="shared" si="2"/>
         <v>11</v>
       </c>
       <c r="T76" s="7"/>
@@ -7906,7 +7903,7 @@
       </c>
       <c r="R77" s="9"/>
       <c r="S77" s="11">
-        <f>IF(R77&lt;&gt;"",R77,ROUND((L77+M77+K77+IF(COUNT(N77:P77)&gt;0,AVERAGE(N77:P77),0))/(3+IF(COUNT(N77:P77)&gt;0,1,0)),1))</f>
+        <f t="shared" si="2"/>
         <v>10.7</v>
       </c>
       <c r="T77" s="7"/>
@@ -7961,7 +7958,7 @@
       <c r="Q78" s="9"/>
       <c r="R78" s="9"/>
       <c r="S78" s="11">
-        <f>IF(R78&lt;&gt;"",R78,ROUND((L78+M78+K78+IF(COUNT(N78:P78)&gt;0,AVERAGE(N78:P78),0))/(3+IF(COUNT(N78:P78)&gt;0,1,0)),1))</f>
+        <f t="shared" si="2"/>
         <v>10.7</v>
       </c>
       <c r="T78" s="7"/>
@@ -7977,7 +7974,7 @@
       <c r="B79" s="8" t="s">
         <v>254</v>
       </c>
-      <c r="C79" s="15" t="s">
+      <c r="C79" s="8" t="s">
         <v>36</v>
       </c>
       <c r="D79" s="8" t="s">
@@ -8018,7 +8015,7 @@
       </c>
       <c r="R79" s="9"/>
       <c r="S79" s="11">
-        <f>IF(R79&lt;&gt;"",R79,ROUND((L79+M79+K79+IF(COUNT(N79:P79)&gt;0,AVERAGE(N79:P79),0))/(3+IF(COUNT(N79:P79)&gt;0,1,0)),1))</f>
+        <f t="shared" si="2"/>
         <v>10.7</v>
       </c>
       <c r="T79" s="7"/>
@@ -8077,7 +8074,7 @@
       </c>
       <c r="R80" s="9"/>
       <c r="S80" s="11">
-        <f>IF(R80&lt;&gt;"",R80,ROUND((L80+M80+K80+IF(COUNT(N80:P80)&gt;0,AVERAGE(N80:P80),0))/(3+IF(COUNT(N80:P80)&gt;0,1,0)),1))</f>
+        <f t="shared" si="2"/>
         <v>10.3</v>
       </c>
       <c r="T80" s="7"/>
@@ -8132,7 +8129,7 @@
       <c r="Q81" s="9"/>
       <c r="R81" s="9"/>
       <c r="S81" s="11">
-        <f>IF(R81&lt;&gt;"",R81,ROUND((L81+M81+K81+IF(COUNT(N81:P81)&gt;0,AVERAGE(N81:P81),0))/(3+IF(COUNT(N81:P81)&gt;0,1,0)),1))</f>
+        <f t="shared" si="2"/>
         <v>10.3</v>
       </c>
       <c r="T81" s="7"/>
@@ -8191,7 +8188,7 @@
       </c>
       <c r="R82" s="9"/>
       <c r="S82" s="11">
-        <f>IF(R82&lt;&gt;"",R82,ROUND((L82+M82+K82+IF(COUNT(N82:P82)&gt;0,AVERAGE(N82:P82),0))/(3+IF(COUNT(N82:P82)&gt;0,1,0)),1))</f>
+        <f t="shared" si="2"/>
         <v>10.3</v>
       </c>
       <c r="T82" s="7"/>
@@ -8246,7 +8243,7 @@
       <c r="Q83" s="9"/>
       <c r="R83" s="9"/>
       <c r="S83" s="11">
-        <f>IF(R83&lt;&gt;"",R83,ROUND((L83+M83+K83+IF(COUNT(N83:P83)&gt;0,AVERAGE(N83:P83),0))/(3+IF(COUNT(N83:P83)&gt;0,1,0)),1))</f>
+        <f t="shared" si="2"/>
         <v>10.3</v>
       </c>
       <c r="T83" s="7"/>
@@ -8305,7 +8302,7 @@
       </c>
       <c r="R84" s="9"/>
       <c r="S84" s="11">
-        <f>IF(R84&lt;&gt;"",R84,ROUND((L84+M84+K84+IF(COUNT(N84:P84)&gt;0,AVERAGE(N84:P84),0))/(3+IF(COUNT(N84:P84)&gt;0,1,0)),1))</f>
+        <f t="shared" si="2"/>
         <v>10.3</v>
       </c>
       <c r="T84" s="7"/>
@@ -8362,7 +8359,7 @@
       </c>
       <c r="R85" s="9"/>
       <c r="S85" s="11">
-        <f>IF(R85&lt;&gt;"",R85,ROUND((L85+M85+K85+IF(COUNT(N85:P85)&gt;0,AVERAGE(N85:P85),0))/(3+IF(COUNT(N85:P85)&gt;0,1,0)),1))</f>
+        <f t="shared" si="2"/>
         <v>10.3</v>
       </c>
       <c r="T85" s="7"/>
@@ -8419,7 +8416,7 @@
       <c r="Q86" s="9"/>
       <c r="R86" s="9"/>
       <c r="S86" s="11">
-        <f>IF(R86&lt;&gt;"",R86,ROUND((L86+M86+K86+IF(COUNT(N86:P86)&gt;0,AVERAGE(N86:P86),0))/(3+IF(COUNT(N86:P86)&gt;0,1,0)),1))</f>
+        <f t="shared" si="2"/>
         <v>10.3</v>
       </c>
       <c r="T86" s="7"/>
@@ -8476,7 +8473,7 @@
         <v>13</v>
       </c>
       <c r="S87" s="11">
-        <f>IF(R87&lt;&gt;"",R87,ROUND((L87+M87+K87+IF(COUNT(N87:P87)&gt;0,AVERAGE(N87:P87),0))/(3+IF(COUNT(N87:P87)&gt;0,1,0)),1))</f>
+        <f t="shared" si="2"/>
         <v>13</v>
       </c>
       <c r="T87" s="7"/>
@@ -8535,7 +8532,7 @@
       </c>
       <c r="R88" s="9"/>
       <c r="S88" s="11">
-        <f>IF(R88&lt;&gt;"",R88,ROUND((L88+M88+K88+IF(COUNT(N88:P88)&gt;0,AVERAGE(N88:P88),0))/(3+IF(COUNT(N88:P88)&gt;0,1,0)),1))</f>
+        <f t="shared" si="2"/>
         <v>10</v>
       </c>
       <c r="T88" s="7"/>
@@ -8551,7 +8548,7 @@
       <c r="B89" s="8" t="s">
         <v>603</v>
       </c>
-      <c r="C89" s="15" t="s">
+      <c r="C89" s="8" t="s">
         <v>36</v>
       </c>
       <c r="D89" s="8" t="s">
@@ -8590,7 +8587,7 @@
       <c r="Q89" s="9"/>
       <c r="R89" s="9"/>
       <c r="S89" s="11">
-        <f>IF(R89&lt;&gt;"",R89,ROUND((L89+M89+K89+IF(COUNT(N89:P89)&gt;0,AVERAGE(N89:P89),0))/(3+IF(COUNT(N89:P89)&gt;0,1,0)),1))</f>
+        <f t="shared" si="2"/>
         <v>9.8000000000000007</v>
       </c>
       <c r="T89" s="7"/>
@@ -8647,7 +8644,7 @@
       <c r="Q90" s="9"/>
       <c r="R90" s="9"/>
       <c r="S90" s="11">
-        <f>IF(R90&lt;&gt;"",R90,ROUND((L90+M90+K90+IF(COUNT(N90:P90)&gt;0,AVERAGE(N90:P90),0))/(3+IF(COUNT(N90:P90)&gt;0,1,0)),1))</f>
+        <f t="shared" si="2"/>
         <v>9.8000000000000007</v>
       </c>
       <c r="T90" s="7"/>
@@ -8704,7 +8701,7 @@
       </c>
       <c r="R91" s="9"/>
       <c r="S91" s="11">
-        <f>IF(R91&lt;&gt;"",R91,ROUND((L91+M91+K91+IF(COUNT(N91:P91)&gt;0,AVERAGE(N91:P91),0))/(3+IF(COUNT(N91:P91)&gt;0,1,0)),1))</f>
+        <f t="shared" si="2"/>
         <v>9.6999999999999993</v>
       </c>
       <c r="T91" s="7"/>
@@ -8759,7 +8756,7 @@
       <c r="Q92" s="9"/>
       <c r="R92" s="9"/>
       <c r="S92" s="11">
-        <f>IF(R92&lt;&gt;"",R92,ROUND((L92+M92+K92+IF(COUNT(N92:P92)&gt;0,AVERAGE(N92:P92),0))/(3+IF(COUNT(N92:P92)&gt;0,1,0)),1))</f>
+        <f t="shared" si="2"/>
         <v>9.6999999999999993</v>
       </c>
       <c r="T92" s="7"/>
@@ -8818,7 +8815,7 @@
       </c>
       <c r="R93" s="9"/>
       <c r="S93" s="11">
-        <f>IF(R93&lt;&gt;"",R93,ROUND((L93+M93+K93+IF(COUNT(N93:P93)&gt;0,AVERAGE(N93:P93),0))/(3+IF(COUNT(N93:P93)&gt;0,1,0)),1))</f>
+        <f t="shared" si="2"/>
         <v>9.5</v>
       </c>
       <c r="T93" s="7"/>
@@ -8871,7 +8868,7 @@
       <c r="Q94" s="9"/>
       <c r="R94" s="9"/>
       <c r="S94" s="11">
-        <f>IF(R94&lt;&gt;"",R94,ROUND((L94+M94+K94+IF(COUNT(N94:P94)&gt;0,AVERAGE(N94:P94),0))/(3+IF(COUNT(N94:P94)&gt;0,1,0)),1))</f>
+        <f t="shared" si="2"/>
         <v>9.3000000000000007</v>
       </c>
       <c r="T94" s="7"/>
@@ -8924,7 +8921,7 @@
       <c r="Q95" s="9"/>
       <c r="R95" s="9"/>
       <c r="S95" s="11">
-        <f>IF(R95&lt;&gt;"",R95,ROUND((L95+M95+K95+IF(COUNT(N95:P95)&gt;0,AVERAGE(N95:P95),0))/(3+IF(COUNT(N95:P95)&gt;0,1,0)),1))</f>
+        <f t="shared" si="2"/>
         <v>9.3000000000000007</v>
       </c>
       <c r="T95" s="7"/>
@@ -8977,7 +8974,7 @@
       <c r="Q96" s="9"/>
       <c r="R96" s="9"/>
       <c r="S96" s="11">
-        <f>IF(R96&lt;&gt;"",R96,ROUND((L96+M96+K96+IF(COUNT(N96:P96)&gt;0,AVERAGE(N96:P96),0))/(3+IF(COUNT(N96:P96)&gt;0,1,0)),1))</f>
+        <f t="shared" si="2"/>
         <v>9.3000000000000007</v>
       </c>
       <c r="T96" s="7"/>
@@ -9030,7 +9027,7 @@
       <c r="Q97" s="9"/>
       <c r="R97" s="9"/>
       <c r="S97" s="11">
-        <f>IF(R97&lt;&gt;"",R97,ROUND((L97+M97+K97+IF(COUNT(N97:P97)&gt;0,AVERAGE(N97:P97),0))/(3+IF(COUNT(N97:P97)&gt;0,1,0)),1))</f>
+        <f t="shared" si="2"/>
         <v>9.3000000000000007</v>
       </c>
       <c r="T97" s="7"/>
@@ -9083,7 +9080,7 @@
       <c r="Q98" s="9"/>
       <c r="R98" s="9"/>
       <c r="S98" s="11">
-        <f>IF(R98&lt;&gt;"",R98,ROUND((L98+M98+K98+IF(COUNT(N98:P98)&gt;0,AVERAGE(N98:P98),0))/(3+IF(COUNT(N98:P98)&gt;0,1,0)),1))</f>
+        <f t="shared" ref="S98:S129" si="3">IF(R98&lt;&gt;"",R98,ROUND((L98+M98+K98+IF(COUNT(N98:P98)&gt;0,AVERAGE(N98:P98),0))/(3+IF(COUNT(N98:P98)&gt;0,1,0)),1))</f>
         <v>9.3000000000000007</v>
       </c>
       <c r="T98" s="7"/>
@@ -9140,7 +9137,7 @@
       </c>
       <c r="R99" s="9"/>
       <c r="S99" s="11">
-        <f>IF(R99&lt;&gt;"",R99,ROUND((L99+M99+K99+IF(COUNT(N99:P99)&gt;0,AVERAGE(N99:P99),0))/(3+IF(COUNT(N99:P99)&gt;0,1,0)),1))</f>
+        <f t="shared" si="3"/>
         <v>9.3000000000000007</v>
       </c>
       <c r="T99" s="7"/>
@@ -9195,7 +9192,7 @@
       <c r="Q100" s="9"/>
       <c r="R100" s="9"/>
       <c r="S100" s="11">
-        <f>IF(R100&lt;&gt;"",R100,ROUND((L100+M100+K100+IF(COUNT(N100:P100)&gt;0,AVERAGE(N100:P100),0))/(3+IF(COUNT(N100:P100)&gt;0,1,0)),1))</f>
+        <f t="shared" si="3"/>
         <v>9.3000000000000007</v>
       </c>
       <c r="T100" s="7"/>
@@ -9250,7 +9247,7 @@
       <c r="Q101" s="9"/>
       <c r="R101" s="9"/>
       <c r="S101" s="11">
-        <f>IF(R101&lt;&gt;"",R101,ROUND((L101+M101+K101+IF(COUNT(N101:P101)&gt;0,AVERAGE(N101:P101),0))/(3+IF(COUNT(N101:P101)&gt;0,1,0)),1))</f>
+        <f t="shared" si="3"/>
         <v>9.3000000000000007</v>
       </c>
       <c r="T101" s="7"/>
@@ -9305,7 +9302,7 @@
       <c r="Q102" s="9"/>
       <c r="R102" s="9"/>
       <c r="S102" s="11">
-        <f>IF(R102&lt;&gt;"",R102,ROUND((L102+M102+K102+IF(COUNT(N102:P102)&gt;0,AVERAGE(N102:P102),0))/(3+IF(COUNT(N102:P102)&gt;0,1,0)),1))</f>
+        <f t="shared" si="3"/>
         <v>9.3000000000000007</v>
       </c>
       <c r="T102" s="7"/>
@@ -9364,7 +9361,7 @@
       </c>
       <c r="R103" s="9"/>
       <c r="S103" s="11">
-        <f>IF(R103&lt;&gt;"",R103,ROUND((L103+M103+K103+IF(COUNT(N103:P103)&gt;0,AVERAGE(N103:P103),0))/(3+IF(COUNT(N103:P103)&gt;0,1,0)),1))</f>
+        <f t="shared" si="3"/>
         <v>9.3000000000000007</v>
       </c>
       <c r="T103" s="7"/>
@@ -9419,7 +9416,7 @@
       <c r="Q104" s="9"/>
       <c r="R104" s="9"/>
       <c r="S104" s="11">
-        <f>IF(R104&lt;&gt;"",R104,ROUND((L104+M104+K104+IF(COUNT(N104:P104)&gt;0,AVERAGE(N104:P104),0))/(3+IF(COUNT(N104:P104)&gt;0,1,0)),1))</f>
+        <f t="shared" si="3"/>
         <v>9</v>
       </c>
       <c r="T104" s="7"/>
@@ -9435,7 +9432,7 @@
       <c r="B105" s="8" t="s">
         <v>703</v>
       </c>
-      <c r="C105" s="15">
+      <c r="C105" s="8">
         <v>20000000</v>
       </c>
       <c r="D105" s="8" t="s">
@@ -9476,7 +9473,7 @@
       </c>
       <c r="R105" s="9"/>
       <c r="S105" s="11">
-        <f>IF(R105&lt;&gt;"",R105,ROUND((L105+M105+K105+IF(COUNT(N105:P105)&gt;0,AVERAGE(N105:P105),0))/(3+IF(COUNT(N105:P105)&gt;0,1,0)),1))</f>
+        <f t="shared" si="3"/>
         <v>9</v>
       </c>
       <c r="T105" s="7"/>
@@ -9533,7 +9530,7 @@
       </c>
       <c r="R106" s="9"/>
       <c r="S106" s="11">
-        <f>IF(R106&lt;&gt;"",R106,ROUND((L106+M106+K106+IF(COUNT(N106:P106)&gt;0,AVERAGE(N106:P106),0))/(3+IF(COUNT(N106:P106)&gt;0,1,0)),1))</f>
+        <f t="shared" si="3"/>
         <v>9</v>
       </c>
       <c r="T106" s="7"/>
@@ -9592,7 +9589,7 @@
       </c>
       <c r="R107" s="9"/>
       <c r="S107" s="11">
-        <f>IF(R107&lt;&gt;"",R107,ROUND((L107+M107+K107+IF(COUNT(N107:P107)&gt;0,AVERAGE(N107:P107),0))/(3+IF(COUNT(N107:P107)&gt;0,1,0)),1))</f>
+        <f t="shared" si="3"/>
         <v>8.8000000000000007</v>
       </c>
       <c r="T107" s="7"/>
@@ -9651,7 +9648,7 @@
       </c>
       <c r="R108" s="9"/>
       <c r="S108" s="11">
-        <f>IF(R108&lt;&gt;"",R108,ROUND((L108+M108+K108+IF(COUNT(N108:P108)&gt;0,AVERAGE(N108:P108),0))/(3+IF(COUNT(N108:P108)&gt;0,1,0)),1))</f>
+        <f t="shared" si="3"/>
         <v>8.8000000000000007</v>
       </c>
       <c r="T108" s="7"/>
@@ -9710,7 +9707,7 @@
       </c>
       <c r="R109" s="9"/>
       <c r="S109" s="11">
-        <f>IF(R109&lt;&gt;"",R109,ROUND((L109+M109+K109+IF(COUNT(N109:P109)&gt;0,AVERAGE(N109:P109),0))/(3+IF(COUNT(N109:P109)&gt;0,1,0)),1))</f>
+        <f t="shared" si="3"/>
         <v>8.8000000000000007</v>
       </c>
       <c r="T109" s="7"/>
@@ -9769,7 +9766,7 @@
       </c>
       <c r="R110" s="9"/>
       <c r="S110" s="11">
-        <f>IF(R110&lt;&gt;"",R110,ROUND((L110+M110+K110+IF(COUNT(N110:P110)&gt;0,AVERAGE(N110:P110),0))/(3+IF(COUNT(N110:P110)&gt;0,1,0)),1))</f>
+        <f t="shared" si="3"/>
         <v>8.8000000000000007</v>
       </c>
       <c r="T110" s="7"/>
@@ -9828,7 +9825,7 @@
       </c>
       <c r="R111" s="9"/>
       <c r="S111" s="11">
-        <f>IF(R111&lt;&gt;"",R111,ROUND((L111+M111+K111+IF(COUNT(N111:P111)&gt;0,AVERAGE(N111:P111),0))/(3+IF(COUNT(N111:P111)&gt;0,1,0)),1))</f>
+        <f t="shared" si="3"/>
         <v>8.8000000000000007</v>
       </c>
       <c r="T111" s="7"/>
@@ -9883,7 +9880,7 @@
       </c>
       <c r="R112" s="9"/>
       <c r="S112" s="11">
-        <f>IF(R112&lt;&gt;"",R112,ROUND((L112+M112+K112+IF(COUNT(N112:P112)&gt;0,AVERAGE(N112:P112),0))/(3+IF(COUNT(N112:P112)&gt;0,1,0)),1))</f>
+        <f t="shared" si="3"/>
         <v>8.6999999999999993</v>
       </c>
       <c r="T112" s="7"/>
@@ -9938,7 +9935,7 @@
       <c r="Q113" s="9"/>
       <c r="R113" s="9"/>
       <c r="S113" s="11">
-        <f>IF(R113&lt;&gt;"",R113,ROUND((L113+M113+K113+IF(COUNT(N113:P113)&gt;0,AVERAGE(N113:P113),0))/(3+IF(COUNT(N113:P113)&gt;0,1,0)),1))</f>
+        <f t="shared" si="3"/>
         <v>8.6999999999999993</v>
       </c>
       <c r="T113" s="7"/>
@@ -9997,7 +9994,7 @@
       </c>
       <c r="R114" s="9"/>
       <c r="S114" s="11">
-        <f>IF(R114&lt;&gt;"",R114,ROUND((L114+M114+K114+IF(COUNT(N114:P114)&gt;0,AVERAGE(N114:P114),0))/(3+IF(COUNT(N114:P114)&gt;0,1,0)),1))</f>
+        <f t="shared" si="3"/>
         <v>8.5</v>
       </c>
       <c r="T114" s="7"/>
@@ -10056,7 +10053,7 @@
       </c>
       <c r="R115" s="9"/>
       <c r="S115" s="11">
-        <f>IF(R115&lt;&gt;"",R115,ROUND((L115+M115+K115+IF(COUNT(N115:P115)&gt;0,AVERAGE(N115:P115),0))/(3+IF(COUNT(N115:P115)&gt;0,1,0)),1))</f>
+        <f t="shared" si="3"/>
         <v>8.5</v>
       </c>
       <c r="T115" s="7"/>
@@ -10113,7 +10110,7 @@
       <c r="Q116" s="9"/>
       <c r="R116" s="9"/>
       <c r="S116" s="11">
-        <f>IF(R116&lt;&gt;"",R116,ROUND((L116+M116+K116+IF(COUNT(N116:P116)&gt;0,AVERAGE(N116:P116),0))/(3+IF(COUNT(N116:P116)&gt;0,1,0)),1))</f>
+        <f t="shared" si="3"/>
         <v>8.3000000000000007</v>
       </c>
       <c r="T116" s="7"/>
@@ -10170,7 +10167,7 @@
       <c r="Q117" s="9"/>
       <c r="R117" s="9"/>
       <c r="S117" s="11">
-        <f>IF(R117&lt;&gt;"",R117,ROUND((L117+M117+K117+IF(COUNT(N117:P117)&gt;0,AVERAGE(N117:P117),0))/(3+IF(COUNT(N117:P117)&gt;0,1,0)),1))</f>
+        <f t="shared" si="3"/>
         <v>8.3000000000000007</v>
       </c>
       <c r="T117" s="7"/>
@@ -10225,7 +10222,7 @@
       <c r="Q118" s="9"/>
       <c r="R118" s="9"/>
       <c r="S118" s="11">
-        <f>IF(R118&lt;&gt;"",R118,ROUND((L118+M118+K118+IF(COUNT(N118:P118)&gt;0,AVERAGE(N118:P118),0))/(3+IF(COUNT(N118:P118)&gt;0,1,0)),1))</f>
+        <f t="shared" si="3"/>
         <v>8.3000000000000007</v>
       </c>
       <c r="T118" s="7"/>
@@ -10241,10 +10238,10 @@
       <c r="B119" s="8" t="s">
         <v>438</v>
       </c>
-      <c r="C119" s="15">
+      <c r="C119" s="8">
         <v>350000000</v>
       </c>
-      <c r="D119" s="15" t="s">
+      <c r="D119" s="8" t="s">
         <v>24</v>
       </c>
       <c r="E119" s="8" t="s">
@@ -10284,7 +10281,7 @@
       </c>
       <c r="R119" s="9"/>
       <c r="S119" s="11">
-        <f>IF(R119&lt;&gt;"",R119,ROUND((L119+M119+K119+IF(COUNT(N119:P119)&gt;0,AVERAGE(N119:P119),0))/(3+IF(COUNT(N119:P119)&gt;0,1,0)),1))</f>
+        <f t="shared" si="3"/>
         <v>8.3000000000000007</v>
       </c>
       <c r="T119" s="7"/>
@@ -10341,7 +10338,7 @@
       <c r="Q120" s="9"/>
       <c r="R120" s="9"/>
       <c r="S120" s="11">
-        <f>IF(R120&lt;&gt;"",R120,ROUND((L120+M120+K120+IF(COUNT(N120:P120)&gt;0,AVERAGE(N120:P120),0))/(3+IF(COUNT(N120:P120)&gt;0,1,0)),1))</f>
+        <f t="shared" si="3"/>
         <v>8.3000000000000007</v>
       </c>
       <c r="T120" s="7"/>
@@ -10400,7 +10397,7 @@
       </c>
       <c r="R121" s="9"/>
       <c r="S121" s="11">
-        <f>IF(R121&lt;&gt;"",R121,ROUND((L121+M121+K121+IF(COUNT(N121:P121)&gt;0,AVERAGE(N121:P121),0))/(3+IF(COUNT(N121:P121)&gt;0,1,0)),1))</f>
+        <f t="shared" si="3"/>
         <v>8.3000000000000007</v>
       </c>
       <c r="T121" s="7"/>
@@ -10455,7 +10452,7 @@
       </c>
       <c r="R122" s="9"/>
       <c r="S122" s="11">
-        <f>IF(R122&lt;&gt;"",R122,ROUND((L122+M122+K122+IF(COUNT(N122:P122)&gt;0,AVERAGE(N122:P122),0))/(3+IF(COUNT(N122:P122)&gt;0,1,0)),1))</f>
+        <f t="shared" si="3"/>
         <v>8</v>
       </c>
       <c r="T122" s="7"/>
@@ -10512,7 +10509,7 @@
         <v>15</v>
       </c>
       <c r="S123" s="11">
-        <f>IF(R123&lt;&gt;"",R123,ROUND((L123+M123+K123+IF(COUNT(N123:P123)&gt;0,AVERAGE(N123:P123),0))/(3+IF(COUNT(N123:P123)&gt;0,1,0)),1))</f>
+        <f t="shared" si="3"/>
         <v>15</v>
       </c>
       <c r="T123" s="7"/>
@@ -10565,7 +10562,7 @@
       <c r="Q124" s="9"/>
       <c r="R124" s="9"/>
       <c r="S124" s="11">
-        <f>IF(R124&lt;&gt;"",R124,ROUND((L124+M124+K124+IF(COUNT(N124:P124)&gt;0,AVERAGE(N124:P124),0))/(3+IF(COUNT(N124:P124)&gt;0,1,0)),1))</f>
+        <f t="shared" si="3"/>
         <v>8</v>
       </c>
       <c r="T124" s="7"/>
@@ -10620,7 +10617,7 @@
       <c r="Q125" s="9"/>
       <c r="R125" s="9"/>
       <c r="S125" s="11">
-        <f>IF(R125&lt;&gt;"",R125,ROUND((L125+M125+K125+IF(COUNT(N125:P125)&gt;0,AVERAGE(N125:P125),0))/(3+IF(COUNT(N125:P125)&gt;0,1,0)),1))</f>
+        <f t="shared" si="3"/>
         <v>8</v>
       </c>
       <c r="T125" s="7"/>
@@ -10675,7 +10672,7 @@
       <c r="Q126" s="9"/>
       <c r="R126" s="9"/>
       <c r="S126" s="11">
-        <f>IF(R126&lt;&gt;"",R126,ROUND((L126+M126+K126+IF(COUNT(N126:P126)&gt;0,AVERAGE(N126:P126),0))/(3+IF(COUNT(N126:P126)&gt;0,1,0)),1))</f>
+        <f t="shared" si="3"/>
         <v>8</v>
       </c>
       <c r="T126" s="7"/>
@@ -10730,7 +10727,7 @@
       <c r="Q127" s="9"/>
       <c r="R127" s="9"/>
       <c r="S127" s="11">
-        <f>IF(R127&lt;&gt;"",R127,ROUND((L127+M127+K127+IF(COUNT(N127:P127)&gt;0,AVERAGE(N127:P127),0))/(3+IF(COUNT(N127:P127)&gt;0,1,0)),1))</f>
+        <f t="shared" si="3"/>
         <v>8</v>
       </c>
       <c r="T127" s="7"/>
@@ -10789,7 +10786,7 @@
       </c>
       <c r="R128" s="9"/>
       <c r="S128" s="11">
-        <f>IF(R128&lt;&gt;"",R128,ROUND((L128+M128+K128+IF(COUNT(N128:P128)&gt;0,AVERAGE(N128:P128),0))/(3+IF(COUNT(N128:P128)&gt;0,1,0)),1))</f>
+        <f t="shared" si="3"/>
         <v>8</v>
       </c>
       <c r="T128" s="7"/>
@@ -10846,7 +10843,7 @@
       </c>
       <c r="R129" s="9"/>
       <c r="S129" s="11">
-        <f>IF(R129&lt;&gt;"",R129,ROUND((L129+M129+K129+IF(COUNT(N129:P129)&gt;0,AVERAGE(N129:P129),0))/(3+IF(COUNT(N129:P129)&gt;0,1,0)),1))</f>
+        <f t="shared" si="3"/>
         <v>8</v>
       </c>
       <c r="T129" s="7"/>
@@ -10901,7 +10898,7 @@
       <c r="Q130" s="9"/>
       <c r="R130" s="9"/>
       <c r="S130" s="11">
-        <f>IF(R130&lt;&gt;"",R130,ROUND((L130+M130+K130+IF(COUNT(N130:P130)&gt;0,AVERAGE(N130:P130),0))/(3+IF(COUNT(N130:P130)&gt;0,1,0)),1))</f>
+        <f t="shared" ref="S130:S161" si="4">IF(R130&lt;&gt;"",R130,ROUND((L130+M130+K130+IF(COUNT(N130:P130)&gt;0,AVERAGE(N130:P130),0))/(3+IF(COUNT(N130:P130)&gt;0,1,0)),1))</f>
         <v>8</v>
       </c>
       <c r="T130" s="7"/>
@@ -10917,7 +10914,7 @@
       <c r="B131" s="8" t="s">
         <v>895</v>
       </c>
-      <c r="C131" s="15" t="s">
+      <c r="C131" s="8" t="s">
         <v>36</v>
       </c>
       <c r="D131" s="8" t="s">
@@ -10958,7 +10955,7 @@
       <c r="Q131" s="9"/>
       <c r="R131" s="9"/>
       <c r="S131" s="11">
-        <f>IF(R131&lt;&gt;"",R131,ROUND((L131+M131+K131+IF(COUNT(N131:P131)&gt;0,AVERAGE(N131:P131),0))/(3+IF(COUNT(N131:P131)&gt;0,1,0)),1))</f>
+        <f t="shared" si="4"/>
         <v>7.8</v>
       </c>
       <c r="T131" s="7"/>
@@ -10974,7 +10971,7 @@
       <c r="B132" s="8" t="s">
         <v>535</v>
       </c>
-      <c r="C132" s="15">
+      <c r="C132" s="8">
         <v>200000000</v>
       </c>
       <c r="D132" s="8" t="s">
@@ -11015,7 +11012,7 @@
       <c r="Q132" s="9"/>
       <c r="R132" s="9"/>
       <c r="S132" s="11">
-        <f>IF(R132&lt;&gt;"",R132,ROUND((L132+M132+K132+IF(COUNT(N132:P132)&gt;0,AVERAGE(N132:P132),0))/(3+IF(COUNT(N132:P132)&gt;0,1,0)),1))</f>
+        <f t="shared" si="4"/>
         <v>7.8</v>
       </c>
       <c r="T132" s="7"/>
@@ -11074,7 +11071,7 @@
       </c>
       <c r="R133" s="9"/>
       <c r="S133" s="11">
-        <f>IF(R133&lt;&gt;"",R133,ROUND((L133+M133+K133+IF(COUNT(N133:P133)&gt;0,AVERAGE(N133:P133),0))/(3+IF(COUNT(N133:P133)&gt;0,1,0)),1))</f>
+        <f t="shared" si="4"/>
         <v>7.8</v>
       </c>
       <c r="T133" s="7"/>
@@ -11131,7 +11128,7 @@
       </c>
       <c r="R134" s="9"/>
       <c r="S134" s="11">
-        <f>IF(R134&lt;&gt;"",R134,ROUND((L134+M134+K134+IF(COUNT(N134:P134)&gt;0,AVERAGE(N134:P134),0))/(3+IF(COUNT(N134:P134)&gt;0,1,0)),1))</f>
+        <f t="shared" si="4"/>
         <v>7.8</v>
       </c>
       <c r="T134" s="7"/>
@@ -11188,7 +11185,7 @@
       </c>
       <c r="R135" s="9"/>
       <c r="S135" s="11">
-        <f>IF(R135&lt;&gt;"",R135,ROUND((L135+M135+K135+IF(COUNT(N135:P135)&gt;0,AVERAGE(N135:P135),0))/(3+IF(COUNT(N135:P135)&gt;0,1,0)),1))</f>
+        <f t="shared" si="4"/>
         <v>7.7</v>
       </c>
       <c r="T135" s="7"/>
@@ -11243,7 +11240,7 @@
       <c r="Q136" s="9"/>
       <c r="R136" s="9"/>
       <c r="S136" s="11">
-        <f>IF(R136&lt;&gt;"",R136,ROUND((L136+M136+K136+IF(COUNT(N136:P136)&gt;0,AVERAGE(N136:P136),0))/(3+IF(COUNT(N136:P136)&gt;0,1,0)),1))</f>
+        <f t="shared" si="4"/>
         <v>7.7</v>
       </c>
       <c r="T136" s="7"/>
@@ -11298,7 +11295,7 @@
       <c r="Q137" s="9"/>
       <c r="R137" s="9"/>
       <c r="S137" s="11">
-        <f>IF(R137&lt;&gt;"",R137,ROUND((L137+M137+K137+IF(COUNT(N137:P137)&gt;0,AVERAGE(N137:P137),0))/(3+IF(COUNT(N137:P137)&gt;0,1,0)),1))</f>
+        <f t="shared" si="4"/>
         <v>7.7</v>
       </c>
       <c r="T137" s="7"/>
@@ -11353,7 +11350,7 @@
       </c>
       <c r="R138" s="9"/>
       <c r="S138" s="11">
-        <f>IF(R138&lt;&gt;"",R138,ROUND((L138+M138+K138+IF(COUNT(N138:P138)&gt;0,AVERAGE(N138:P138),0))/(3+IF(COUNT(N138:P138)&gt;0,1,0)),1))</f>
+        <f t="shared" si="4"/>
         <v>7.3</v>
       </c>
       <c r="T138" s="7"/>
@@ -11410,7 +11407,7 @@
       </c>
       <c r="R139" s="9"/>
       <c r="S139" s="11">
-        <f>IF(R139&lt;&gt;"",R139,ROUND((L139+M139+K139+IF(COUNT(N139:P139)&gt;0,AVERAGE(N139:P139),0))/(3+IF(COUNT(N139:P139)&gt;0,1,0)),1))</f>
+        <f t="shared" si="4"/>
         <v>7.3</v>
       </c>
       <c r="T139" s="7"/>
@@ -11467,7 +11464,7 @@
       <c r="Q140" s="9"/>
       <c r="R140" s="9"/>
       <c r="S140" s="11">
-        <f>IF(R140&lt;&gt;"",R140,ROUND((L140+M140+K140+IF(COUNT(N140:P140)&gt;0,AVERAGE(N140:P140),0))/(3+IF(COUNT(N140:P140)&gt;0,1,0)),1))</f>
+        <f t="shared" si="4"/>
         <v>7.3</v>
       </c>
       <c r="T140" s="7"/>
@@ -11526,7 +11523,7 @@
       </c>
       <c r="R141" s="9"/>
       <c r="S141" s="11">
-        <f>IF(R141&lt;&gt;"",R141,ROUND((L141+M141+K141+IF(COUNT(N141:P141)&gt;0,AVERAGE(N141:P141),0))/(3+IF(COUNT(N141:P141)&gt;0,1,0)),1))</f>
+        <f t="shared" si="4"/>
         <v>7.3</v>
       </c>
       <c r="T141" s="7"/>
@@ -11581,7 +11578,7 @@
       <c r="Q142" s="9"/>
       <c r="R142" s="9"/>
       <c r="S142" s="11">
-        <f>IF(R142&lt;&gt;"",R142,ROUND((L142+M142+K142+IF(COUNT(N142:P142)&gt;0,AVERAGE(N142:P142),0))/(3+IF(COUNT(N142:P142)&gt;0,1,0)),1))</f>
+        <f t="shared" si="4"/>
         <v>7.3</v>
       </c>
       <c r="T142" s="7"/>
@@ -11597,10 +11594,10 @@
       <c r="B143" s="8" t="s">
         <v>695</v>
       </c>
-      <c r="C143" s="15">
+      <c r="C143" s="8">
         <v>17000000</v>
       </c>
-      <c r="D143" s="15" t="s">
+      <c r="D143" s="8" t="s">
         <v>125</v>
       </c>
       <c r="E143" s="8" t="s">
@@ -11638,7 +11635,7 @@
       </c>
       <c r="R143" s="9"/>
       <c r="S143" s="11">
-        <f>IF(R143&lt;&gt;"",R143,ROUND((L143+M143+K143+IF(COUNT(N143:P143)&gt;0,AVERAGE(N143:P143),0))/(3+IF(COUNT(N143:P143)&gt;0,1,0)),1))</f>
+        <f t="shared" si="4"/>
         <v>7</v>
       </c>
       <c r="T143" s="7"/>
@@ -11691,7 +11688,7 @@
       <c r="Q144" s="9"/>
       <c r="R144" s="9"/>
       <c r="S144" s="11">
-        <f>IF(R144&lt;&gt;"",R144,ROUND((L144+M144+K144+IF(COUNT(N144:P144)&gt;0,AVERAGE(N144:P144),0))/(3+IF(COUNT(N144:P144)&gt;0,1,0)),1))</f>
+        <f t="shared" si="4"/>
         <v>7</v>
       </c>
       <c r="T144" s="7"/>
@@ -11746,7 +11743,7 @@
       <c r="Q145" s="9"/>
       <c r="R145" s="9"/>
       <c r="S145" s="11">
-        <f>IF(R145&lt;&gt;"",R145,ROUND((L145+M145+K145+IF(COUNT(N145:P145)&gt;0,AVERAGE(N145:P145),0))/(3+IF(COUNT(N145:P145)&gt;0,1,0)),1))</f>
+        <f t="shared" si="4"/>
         <v>7</v>
       </c>
       <c r="T145" s="7"/>
@@ -11803,7 +11800,7 @@
       </c>
       <c r="R146" s="9"/>
       <c r="S146" s="11">
-        <f>IF(R146&lt;&gt;"",R146,ROUND((L146+M146+K146+IF(COUNT(N146:P146)&gt;0,AVERAGE(N146:P146),0))/(3+IF(COUNT(N146:P146)&gt;0,1,0)),1))</f>
+        <f t="shared" si="4"/>
         <v>7</v>
       </c>
       <c r="T146" s="7"/>
@@ -11862,7 +11859,7 @@
       </c>
       <c r="R147" s="9"/>
       <c r="S147" s="11">
-        <f>IF(R147&lt;&gt;"",R147,ROUND((L147+M147+K147+IF(COUNT(N147:P147)&gt;0,AVERAGE(N147:P147),0))/(3+IF(COUNT(N147:P147)&gt;0,1,0)),1))</f>
+        <f t="shared" si="4"/>
         <v>7</v>
       </c>
       <c r="T147" s="7"/>
@@ -11919,7 +11916,7 @@
       </c>
       <c r="R148" s="9"/>
       <c r="S148" s="11">
-        <f>IF(R148&lt;&gt;"",R148,ROUND((L148+M148+K148+IF(COUNT(N148:P148)&gt;0,AVERAGE(N148:P148),0))/(3+IF(COUNT(N148:P148)&gt;0,1,0)),1))</f>
+        <f t="shared" si="4"/>
         <v>7</v>
       </c>
       <c r="T148" s="7"/>
@@ -11974,7 +11971,7 @@
       <c r="Q149" s="9"/>
       <c r="R149" s="9"/>
       <c r="S149" s="11">
-        <f>IF(R149&lt;&gt;"",R149,ROUND((L149+M149+K149+IF(COUNT(N149:P149)&gt;0,AVERAGE(N149:P149),0))/(3+IF(COUNT(N149:P149)&gt;0,1,0)),1))</f>
+        <f t="shared" si="4"/>
         <v>6.8</v>
       </c>
       <c r="T149" s="7"/>
@@ -12033,7 +12030,7 @@
       </c>
       <c r="R150" s="9"/>
       <c r="S150" s="11">
-        <f>IF(R150&lt;&gt;"",R150,ROUND((L150+M150+K150+IF(COUNT(N150:P150)&gt;0,AVERAGE(N150:P150),0))/(3+IF(COUNT(N150:P150)&gt;0,1,0)),1))</f>
+        <f t="shared" si="4"/>
         <v>6.8</v>
       </c>
       <c r="T150" s="7"/>
@@ -12088,7 +12085,7 @@
       <c r="Q151" s="9"/>
       <c r="R151" s="9"/>
       <c r="S151" s="11">
-        <f>IF(R151&lt;&gt;"",R151,ROUND((L151+M151+K151+IF(COUNT(N151:P151)&gt;0,AVERAGE(N151:P151),0))/(3+IF(COUNT(N151:P151)&gt;0,1,0)),1))</f>
+        <f t="shared" si="4"/>
         <v>6.7</v>
       </c>
       <c r="T151" s="7"/>
@@ -12145,7 +12142,7 @@
       </c>
       <c r="R152" s="9"/>
       <c r="S152" s="11">
-        <f>IF(R152&lt;&gt;"",R152,ROUND((L152+M152+K152+IF(COUNT(N152:P152)&gt;0,AVERAGE(N152:P152),0))/(3+IF(COUNT(N152:P152)&gt;0,1,0)),1))</f>
+        <f t="shared" si="4"/>
         <v>6.7</v>
       </c>
       <c r="T152" s="7"/>
@@ -12204,7 +12201,7 @@
       </c>
       <c r="R153" s="9"/>
       <c r="S153" s="11">
-        <f>IF(R153&lt;&gt;"",R153,ROUND((L153+M153+K153+IF(COUNT(N153:P153)&gt;0,AVERAGE(N153:P153),0))/(3+IF(COUNT(N153:P153)&gt;0,1,0)),1))</f>
+        <f t="shared" si="4"/>
         <v>6.5</v>
       </c>
       <c r="T153" s="7"/>
@@ -12261,7 +12258,7 @@
       <c r="Q154" s="9"/>
       <c r="R154" s="9"/>
       <c r="S154" s="11">
-        <f>IF(R154&lt;&gt;"",R154,ROUND((L154+M154+K154+IF(COUNT(N154:P154)&gt;0,AVERAGE(N154:P154),0))/(3+IF(COUNT(N154:P154)&gt;0,1,0)),1))</f>
+        <f t="shared" si="4"/>
         <v>6.5</v>
       </c>
       <c r="T154" s="7"/>
@@ -12316,7 +12313,7 @@
       <c r="Q155" s="9"/>
       <c r="R155" s="9"/>
       <c r="S155" s="11">
-        <f>IF(R155&lt;&gt;"",R155,ROUND((L155+M155+K155+IF(COUNT(N155:P155)&gt;0,AVERAGE(N155:P155),0))/(3+IF(COUNT(N155:P155)&gt;0,1,0)),1))</f>
+        <f t="shared" si="4"/>
         <v>6.3</v>
       </c>
       <c r="T155" s="7"/>
@@ -12371,7 +12368,7 @@
       <c r="Q156" s="9"/>
       <c r="R156" s="9"/>
       <c r="S156" s="11">
-        <f>IF(R156&lt;&gt;"",R156,ROUND((L156+M156+K156+IF(COUNT(N156:P156)&gt;0,AVERAGE(N156:P156),0))/(3+IF(COUNT(N156:P156)&gt;0,1,0)),1))</f>
+        <f t="shared" si="4"/>
         <v>6.3</v>
       </c>
       <c r="T156" s="7"/>
@@ -12428,7 +12425,7 @@
         <v>14</v>
       </c>
       <c r="S157" s="11">
-        <f>IF(R157&lt;&gt;"",R157,ROUND((L157+M157+K157+IF(COUNT(N157:P157)&gt;0,AVERAGE(N157:P157),0))/(3+IF(COUNT(N157:P157)&gt;0,1,0)),1))</f>
+        <f t="shared" si="4"/>
         <v>14</v>
       </c>
       <c r="T157" s="7"/>
@@ -12483,7 +12480,7 @@
       <c r="Q158" s="9"/>
       <c r="R158" s="9"/>
       <c r="S158" s="11">
-        <f>IF(R158&lt;&gt;"",R158,ROUND((L158+M158+K158+IF(COUNT(N158:P158)&gt;0,AVERAGE(N158:P158),0))/(3+IF(COUNT(N158:P158)&gt;0,1,0)),1))</f>
+        <f t="shared" si="4"/>
         <v>6.3</v>
       </c>
       <c r="T158" s="7"/>
@@ -12538,7 +12535,7 @@
       <c r="Q159" s="9"/>
       <c r="R159" s="9"/>
       <c r="S159" s="11">
-        <f>IF(R159&lt;&gt;"",R159,ROUND((L159+M159+K159+IF(COUNT(N159:P159)&gt;0,AVERAGE(N159:P159),0))/(3+IF(COUNT(N159:P159)&gt;0,1,0)),1))</f>
+        <f t="shared" si="4"/>
         <v>6.3</v>
       </c>
       <c r="T159" s="7"/>
@@ -12593,7 +12590,7 @@
       </c>
       <c r="R160" s="9"/>
       <c r="S160" s="11">
-        <f>IF(R160&lt;&gt;"",R160,ROUND((L160+M160+K160+IF(COUNT(N160:P160)&gt;0,AVERAGE(N160:P160),0))/(3+IF(COUNT(N160:P160)&gt;0,1,0)),1))</f>
+        <f t="shared" si="4"/>
         <v>6.3</v>
       </c>
       <c r="T160" s="7"/>
@@ -12650,7 +12647,7 @@
       <c r="Q161" s="9"/>
       <c r="R161" s="9"/>
       <c r="S161" s="11">
-        <f>IF(R161&lt;&gt;"",R161,ROUND((L161+M161+K161+IF(COUNT(N161:P161)&gt;0,AVERAGE(N161:P161),0))/(3+IF(COUNT(N161:P161)&gt;0,1,0)),1))</f>
+        <f t="shared" si="4"/>
         <v>6.3</v>
       </c>
       <c r="T161" s="7"/>
@@ -12707,7 +12704,7 @@
       <c r="Q162" s="9"/>
       <c r="R162" s="9"/>
       <c r="S162" s="11">
-        <f>IF(R162&lt;&gt;"",R162,ROUND((L162+M162+K162+IF(COUNT(N162:P162)&gt;0,AVERAGE(N162:P162),0))/(3+IF(COUNT(N162:P162)&gt;0,1,0)),1))</f>
+        <f t="shared" ref="S162:S193" si="5">IF(R162&lt;&gt;"",R162,ROUND((L162+M162+K162+IF(COUNT(N162:P162)&gt;0,AVERAGE(N162:P162),0))/(3+IF(COUNT(N162:P162)&gt;0,1,0)),1))</f>
         <v>6.3</v>
       </c>
       <c r="T162" s="7"/>
@@ -12760,7 +12757,7 @@
       <c r="Q163" s="9"/>
       <c r="R163" s="9"/>
       <c r="S163" s="11">
-        <f>IF(R163&lt;&gt;"",R163,ROUND((L163+M163+K163+IF(COUNT(N163:P163)&gt;0,AVERAGE(N163:P163),0))/(3+IF(COUNT(N163:P163)&gt;0,1,0)),1))</f>
+        <f t="shared" si="5"/>
         <v>6</v>
       </c>
       <c r="T163" s="7"/>
@@ -12813,7 +12810,7 @@
       <c r="Q164" s="9"/>
       <c r="R164" s="9"/>
       <c r="S164" s="11">
-        <f>IF(R164&lt;&gt;"",R164,ROUND((L164+M164+K164+IF(COUNT(N164:P164)&gt;0,AVERAGE(N164:P164),0))/(3+IF(COUNT(N164:P164)&gt;0,1,0)),1))</f>
+        <f t="shared" si="5"/>
         <v>6</v>
       </c>
       <c r="T164" s="7"/>
@@ -12872,7 +12869,7 @@
       </c>
       <c r="R165" s="9"/>
       <c r="S165" s="11">
-        <f>IF(R165&lt;&gt;"",R165,ROUND((L165+M165+K165+IF(COUNT(N165:P165)&gt;0,AVERAGE(N165:P165),0))/(3+IF(COUNT(N165:P165)&gt;0,1,0)),1))</f>
+        <f t="shared" si="5"/>
         <v>5.8</v>
       </c>
       <c r="T165" s="7"/>
@@ -12931,7 +12928,7 @@
       </c>
       <c r="R166" s="9"/>
       <c r="S166" s="11">
-        <f>IF(R166&lt;&gt;"",R166,ROUND((L166+M166+K166+IF(COUNT(N166:P166)&gt;0,AVERAGE(N166:P166),0))/(3+IF(COUNT(N166:P166)&gt;0,1,0)),1))</f>
+        <f t="shared" si="5"/>
         <v>5.8</v>
       </c>
       <c r="T166" s="7"/>
@@ -12988,7 +12985,7 @@
       </c>
       <c r="R167" s="9"/>
       <c r="S167" s="11">
-        <f>IF(R167&lt;&gt;"",R167,ROUND((L167+M167+K167+IF(COUNT(N167:P167)&gt;0,AVERAGE(N167:P167),0))/(3+IF(COUNT(N167:P167)&gt;0,1,0)),1))</f>
+        <f t="shared" si="5"/>
         <v>5.8</v>
       </c>
       <c r="T167" s="7"/>
@@ -13045,7 +13042,7 @@
       </c>
       <c r="R168" s="9"/>
       <c r="S168" s="11">
-        <f>IF(R168&lt;&gt;"",R168,ROUND((L168+M168+K168+IF(COUNT(N168:P168)&gt;0,AVERAGE(N168:P168),0))/(3+IF(COUNT(N168:P168)&gt;0,1,0)),1))</f>
+        <f t="shared" si="5"/>
         <v>5.7</v>
       </c>
       <c r="T168" s="7"/>
@@ -13102,7 +13099,7 @@
       </c>
       <c r="R169" s="9"/>
       <c r="S169" s="11">
-        <f>IF(R169&lt;&gt;"",R169,ROUND((L169+M169+K169+IF(COUNT(N169:P169)&gt;0,AVERAGE(N169:P169),0))/(3+IF(COUNT(N169:P169)&gt;0,1,0)),1))</f>
+        <f t="shared" si="5"/>
         <v>5.7</v>
       </c>
       <c r="T169" s="7"/>
@@ -13157,7 +13154,7 @@
       <c r="Q170" s="9"/>
       <c r="R170" s="9"/>
       <c r="S170" s="11">
-        <f>IF(R170&lt;&gt;"",R170,ROUND((L170+M170+K170+IF(COUNT(N170:P170)&gt;0,AVERAGE(N170:P170),0))/(3+IF(COUNT(N170:P170)&gt;0,1,0)),1))</f>
+        <f t="shared" si="5"/>
         <v>5.3</v>
       </c>
       <c r="T170" s="7"/>
@@ -13214,7 +13211,7 @@
       </c>
       <c r="R171" s="9"/>
       <c r="S171" s="11">
-        <f>IF(R171&lt;&gt;"",R171,ROUND((L171+M171+K171+IF(COUNT(N171:P171)&gt;0,AVERAGE(N171:P171),0))/(3+IF(COUNT(N171:P171)&gt;0,1,0)),1))</f>
+        <f t="shared" si="5"/>
         <v>5.3</v>
       </c>
       <c r="T171" s="7"/>
@@ -13271,7 +13268,7 @@
       </c>
       <c r="R172" s="9"/>
       <c r="S172" s="11">
-        <f>IF(R172&lt;&gt;"",R172,ROUND((L172+M172+K172+IF(COUNT(N172:P172)&gt;0,AVERAGE(N172:P172),0))/(3+IF(COUNT(N172:P172)&gt;0,1,0)),1))</f>
+        <f t="shared" si="5"/>
         <v>5.3</v>
       </c>
       <c r="T172" s="7"/>
@@ -13328,7 +13325,7 @@
       </c>
       <c r="R173" s="9"/>
       <c r="S173" s="11">
-        <f>IF(R173&lt;&gt;"",R173,ROUND((L173+M173+K173+IF(COUNT(N173:P173)&gt;0,AVERAGE(N173:P173),0))/(3+IF(COUNT(N173:P173)&gt;0,1,0)),1))</f>
+        <f t="shared" si="5"/>
         <v>5.3</v>
       </c>
       <c r="T173" s="7"/>
@@ -13385,7 +13382,7 @@
       </c>
       <c r="R174" s="9"/>
       <c r="S174" s="11">
-        <f>IF(R174&lt;&gt;"",R174,ROUND((L174+M174+K174+IF(COUNT(N174:P174)&gt;0,AVERAGE(N174:P174),0))/(3+IF(COUNT(N174:P174)&gt;0,1,0)),1))</f>
+        <f t="shared" si="5"/>
         <v>5.3</v>
       </c>
       <c r="T174" s="7"/>
@@ -13442,7 +13439,7 @@
       <c r="Q175" s="9"/>
       <c r="R175" s="9"/>
       <c r="S175" s="11">
-        <f>IF(R175&lt;&gt;"",R175,ROUND((L175+M175+K175+IF(COUNT(N175:P175)&gt;0,AVERAGE(N175:P175),0))/(3+IF(COUNT(N175:P175)&gt;0,1,0)),1))</f>
+        <f t="shared" si="5"/>
         <v>5.3</v>
       </c>
       <c r="T175" s="7"/>
@@ -13499,7 +13496,7 @@
       </c>
       <c r="R176" s="9"/>
       <c r="S176" s="11">
-        <f>IF(R176&lt;&gt;"",R176,ROUND((L176+M176+K176+IF(COUNT(N176:P176)&gt;0,AVERAGE(N176:P176),0))/(3+IF(COUNT(N176:P176)&gt;0,1,0)),1))</f>
+        <f t="shared" si="5"/>
         <v>5</v>
       </c>
       <c r="T176" s="7"/>
@@ -13554,7 +13551,7 @@
       <c r="Q177" s="9"/>
       <c r="R177" s="9"/>
       <c r="S177" s="11">
-        <f>IF(R177&lt;&gt;"",R177,ROUND((L177+M177+K177+IF(COUNT(N177:P177)&gt;0,AVERAGE(N177:P177),0))/(3+IF(COUNT(N177:P177)&gt;0,1,0)),1))</f>
+        <f t="shared" si="5"/>
         <v>5</v>
       </c>
       <c r="T177" s="7"/>
@@ -13611,7 +13608,7 @@
       </c>
       <c r="R178" s="9"/>
       <c r="S178" s="11">
-        <f>IF(R178&lt;&gt;"",R178,ROUND((L178+M178+K178+IF(COUNT(N178:P178)&gt;0,AVERAGE(N178:P178),0))/(3+IF(COUNT(N178:P178)&gt;0,1,0)),1))</f>
+        <f t="shared" si="5"/>
         <v>5</v>
       </c>
       <c r="T178" s="7"/>
@@ -13670,7 +13667,7 @@
       </c>
       <c r="R179" s="9"/>
       <c r="S179" s="11">
-        <f>IF(R179&lt;&gt;"",R179,ROUND((L179+M179+K179+IF(COUNT(N179:P179)&gt;0,AVERAGE(N179:P179),0))/(3+IF(COUNT(N179:P179)&gt;0,1,0)),1))</f>
+        <f t="shared" si="5"/>
         <v>5</v>
       </c>
       <c r="T179" s="7"/>
@@ -13725,7 +13722,7 @@
       <c r="Q180" s="9"/>
       <c r="R180" s="9"/>
       <c r="S180" s="11">
-        <f>IF(R180&lt;&gt;"",R180,ROUND((L180+M180+K180+IF(COUNT(N180:P180)&gt;0,AVERAGE(N180:P180),0))/(3+IF(COUNT(N180:P180)&gt;0,1,0)),1))</f>
+        <f t="shared" si="5"/>
         <v>5</v>
       </c>
       <c r="T180" s="7"/>
@@ -13784,7 +13781,7 @@
       </c>
       <c r="R181" s="9"/>
       <c r="S181" s="11">
-        <f>IF(R181&lt;&gt;"",R181,ROUND((L181+M181+K181+IF(COUNT(N181:P181)&gt;0,AVERAGE(N181:P181),0))/(3+IF(COUNT(N181:P181)&gt;0,1,0)),1))</f>
+        <f t="shared" si="5"/>
         <v>5</v>
       </c>
       <c r="T181" s="7"/>
@@ -13839,7 +13836,7 @@
       <c r="Q182" s="9"/>
       <c r="R182" s="9"/>
       <c r="S182" s="11">
-        <f>IF(R182&lt;&gt;"",R182,ROUND((L182+M182+K182+IF(COUNT(N182:P182)&gt;0,AVERAGE(N182:P182),0))/(3+IF(COUNT(N182:P182)&gt;0,1,0)),1))</f>
+        <f t="shared" si="5"/>
         <v>4.7</v>
       </c>
       <c r="T182" s="7"/>
@@ -13896,7 +13893,7 @@
       </c>
       <c r="R183" s="9"/>
       <c r="S183" s="11">
-        <f>IF(R183&lt;&gt;"",R183,ROUND((L183+M183+K183+IF(COUNT(N183:P183)&gt;0,AVERAGE(N183:P183),0))/(3+IF(COUNT(N183:P183)&gt;0,1,0)),1))</f>
+        <f t="shared" si="5"/>
         <v>4.3</v>
       </c>
       <c r="T183" s="7"/>
@@ -13951,7 +13948,7 @@
       <c r="Q184" s="9"/>
       <c r="R184" s="9"/>
       <c r="S184" s="11">
-        <f>IF(R184&lt;&gt;"",R184,ROUND((L184+M184+K184+IF(COUNT(N184:P184)&gt;0,AVERAGE(N184:P184),0))/(3+IF(COUNT(N184:P184)&gt;0,1,0)),1))</f>
+        <f t="shared" si="5"/>
         <v>4.3</v>
       </c>
       <c r="T184" s="7"/>
@@ -14006,7 +14003,7 @@
       <c r="Q185" s="9"/>
       <c r="R185" s="9"/>
       <c r="S185" s="11">
-        <f>IF(R185&lt;&gt;"",R185,ROUND((L185+M185+K185+IF(COUNT(N185:P185)&gt;0,AVERAGE(N185:P185),0))/(3+IF(COUNT(N185:P185)&gt;0,1,0)),1))</f>
+        <f t="shared" si="5"/>
         <v>4.3</v>
       </c>
       <c r="T185" s="7"/>
@@ -14061,7 +14058,7 @@
       <c r="Q186" s="9"/>
       <c r="R186" s="9"/>
       <c r="S186" s="11">
-        <f>IF(R186&lt;&gt;"",R186,ROUND((L186+M186+K186+IF(COUNT(N186:P186)&gt;0,AVERAGE(N186:P186),0))/(3+IF(COUNT(N186:P186)&gt;0,1,0)),1))</f>
+        <f t="shared" si="5"/>
         <v>4.3</v>
       </c>
       <c r="T186" s="7"/>
@@ -14110,14 +14107,16 @@
       <c r="M187" s="9"/>
       <c r="N187" s="9"/>
       <c r="O187" s="9"/>
-      <c r="P187" s="9"/>
+      <c r="P187" s="9">
+        <v>5</v>
+      </c>
       <c r="Q187" s="9">
         <v>9</v>
       </c>
       <c r="R187" s="9"/>
       <c r="S187" s="11">
-        <f>IF(R187&lt;&gt;"",R187,ROUND((L187+M187+K187+IF(COUNT(N187:P187)&gt;0,AVERAGE(N187:P187),0))/(3+IF(COUNT(N187:P187)&gt;0,1,0)),1))</f>
-        <v>4.3</v>
+        <f t="shared" si="5"/>
+        <v>4.5</v>
       </c>
       <c r="T187" s="7"/>
       <c r="U187" s="7"/>
@@ -14171,7 +14170,7 @@
       <c r="Q188" s="9"/>
       <c r="R188" s="9"/>
       <c r="S188" s="11">
-        <f>IF(R188&lt;&gt;"",R188,ROUND((L188+M188+K188+IF(COUNT(N188:P188)&gt;0,AVERAGE(N188:P188),0))/(3+IF(COUNT(N188:P188)&gt;0,1,0)),1))</f>
+        <f t="shared" si="5"/>
         <v>4.3</v>
       </c>
       <c r="T188" s="7"/>
@@ -14228,7 +14227,7 @@
       </c>
       <c r="R189" s="9"/>
       <c r="S189" s="11">
-        <f>IF(R189&lt;&gt;"",R189,ROUND((L189+M189+K189+IF(COUNT(N189:P189)&gt;0,AVERAGE(N189:P189),0))/(3+IF(COUNT(N189:P189)&gt;0,1,0)),1))</f>
+        <f t="shared" si="5"/>
         <v>4</v>
       </c>
       <c r="T189" s="7"/>
@@ -14285,7 +14284,7 @@
       </c>
       <c r="R190" s="9"/>
       <c r="S190" s="11">
-        <f>IF(R190&lt;&gt;"",R190,ROUND((L190+M190+K190+IF(COUNT(N190:P190)&gt;0,AVERAGE(N190:P190),0))/(3+IF(COUNT(N190:P190)&gt;0,1,0)),1))</f>
+        <f t="shared" si="5"/>
         <v>4</v>
       </c>
       <c r="T190" s="7"/>
@@ -14344,7 +14343,7 @@
       </c>
       <c r="R191" s="9"/>
       <c r="S191" s="11">
-        <f>IF(R191&lt;&gt;"",R191,ROUND((L191+M191+K191+IF(COUNT(N191:P191)&gt;0,AVERAGE(N191:P191),0))/(3+IF(COUNT(N191:P191)&gt;0,1,0)),1))</f>
+        <f t="shared" si="5"/>
         <v>4</v>
       </c>
       <c r="T191" s="7"/>
@@ -14399,7 +14398,7 @@
       <c r="Q192" s="9"/>
       <c r="R192" s="9"/>
       <c r="S192" s="11">
-        <f>IF(R192&lt;&gt;"",R192,ROUND((L192+M192+K192+IF(COUNT(N192:P192)&gt;0,AVERAGE(N192:P192),0))/(3+IF(COUNT(N192:P192)&gt;0,1,0)),1))</f>
+        <f t="shared" si="5"/>
         <v>4</v>
       </c>
       <c r="T192" s="7"/>
@@ -14452,7 +14451,7 @@
       <c r="Q193" s="9"/>
       <c r="R193" s="9"/>
       <c r="S193" s="11">
-        <f>IF(R193&lt;&gt;"",R193,ROUND((L193+M193+K193+IF(COUNT(N193:P193)&gt;0,AVERAGE(N193:P193),0))/(3+IF(COUNT(N193:P193)&gt;0,1,0)),1))</f>
+        <f t="shared" si="5"/>
         <v>4</v>
       </c>
       <c r="T193" s="7"/>
@@ -14507,7 +14506,7 @@
       <c r="Q194" s="9"/>
       <c r="R194" s="9"/>
       <c r="S194" s="11">
-        <f>IF(R194&lt;&gt;"",R194,ROUND((L194+M194+K194+IF(COUNT(N194:P194)&gt;0,AVERAGE(N194:P194),0))/(3+IF(COUNT(N194:P194)&gt;0,1,0)),1))</f>
+        <f t="shared" ref="S194:S225" si="6">IF(R194&lt;&gt;"",R194,ROUND((L194+M194+K194+IF(COUNT(N194:P194)&gt;0,AVERAGE(N194:P194),0))/(3+IF(COUNT(N194:P194)&gt;0,1,0)),1))</f>
         <v>4</v>
       </c>
       <c r="T194" s="7"/>
@@ -14562,7 +14561,7 @@
       <c r="Q195" s="9"/>
       <c r="R195" s="9"/>
       <c r="S195" s="11">
-        <f>IF(R195&lt;&gt;"",R195,ROUND((L195+M195+K195+IF(COUNT(N195:P195)&gt;0,AVERAGE(N195:P195),0))/(3+IF(COUNT(N195:P195)&gt;0,1,0)),1))</f>
+        <f t="shared" si="6"/>
         <v>4</v>
       </c>
       <c r="T195" s="7"/>
@@ -14619,7 +14618,7 @@
       <c r="Q196" s="9"/>
       <c r="R196" s="9"/>
       <c r="S196" s="11">
-        <f>IF(R196&lt;&gt;"",R196,ROUND((L196+M196+K196+IF(COUNT(N196:P196)&gt;0,AVERAGE(N196:P196),0))/(3+IF(COUNT(N196:P196)&gt;0,1,0)),1))</f>
+        <f t="shared" si="6"/>
         <v>4</v>
       </c>
       <c r="T196" s="7"/>
@@ -14674,7 +14673,7 @@
       <c r="Q197" s="9"/>
       <c r="R197" s="9"/>
       <c r="S197" s="11">
-        <f>IF(R197&lt;&gt;"",R197,ROUND((L197+M197+K197+IF(COUNT(N197:P197)&gt;0,AVERAGE(N197:P197),0))/(3+IF(COUNT(N197:P197)&gt;0,1,0)),1))</f>
+        <f t="shared" si="6"/>
         <v>3.7</v>
       </c>
       <c r="T197" s="7"/>
@@ -14729,7 +14728,7 @@
       <c r="Q198" s="9"/>
       <c r="R198" s="9"/>
       <c r="S198" s="11">
-        <f>IF(R198&lt;&gt;"",R198,ROUND((L198+M198+K198+IF(COUNT(N198:P198)&gt;0,AVERAGE(N198:P198),0))/(3+IF(COUNT(N198:P198)&gt;0,1,0)),1))</f>
+        <f t="shared" si="6"/>
         <v>3.7</v>
       </c>
       <c r="T198" s="7"/>
@@ -14784,7 +14783,7 @@
       <c r="Q199" s="9"/>
       <c r="R199" s="9"/>
       <c r="S199" s="11">
-        <f>IF(R199&lt;&gt;"",R199,ROUND((L199+M199+K199+IF(COUNT(N199:P199)&gt;0,AVERAGE(N199:P199),0))/(3+IF(COUNT(N199:P199)&gt;0,1,0)),1))</f>
+        <f t="shared" si="6"/>
         <v>3.7</v>
       </c>
       <c r="T199" s="7"/>
@@ -14843,7 +14842,7 @@
       </c>
       <c r="R200" s="9"/>
       <c r="S200" s="11">
-        <f>IF(R200&lt;&gt;"",R200,ROUND((L200+M200+K200+IF(COUNT(N200:P200)&gt;0,AVERAGE(N200:P200),0))/(3+IF(COUNT(N200:P200)&gt;0,1,0)),1))</f>
+        <f t="shared" si="6"/>
         <v>2.5</v>
       </c>
       <c r="T200" s="7"/>
@@ -14898,7 +14897,7 @@
       <c r="Q201" s="9"/>
       <c r="R201" s="9"/>
       <c r="S201" s="11">
-        <f>IF(R201&lt;&gt;"",R201,ROUND((L201+M201+K201+IF(COUNT(N201:P201)&gt;0,AVERAGE(N201:P201),0))/(3+IF(COUNT(N201:P201)&gt;0,1,0)),1))</f>
+        <f t="shared" si="6"/>
         <v>2</v>
       </c>
       <c r="T201" s="7"/>
